--- a/assets/excel/2026_1-3-3.xlsx
+++ b/assets/excel/2026_1-3-3.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC102BB-9B5D-4B87-9C6A-3AF2212BD99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0A6C9B-7126-4BA2-8DA8-376543C74A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{73DE4BD7-C5E9-4923-928A-90D02D9B815D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{73DE4BD7-C5E9-4923-928A-90D02D9B815D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,19 +40,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="28">
   <si>
     <t>Indikator 1.3.3: Menschen mit Zuwanderungsgeschichte nach Altersgruppen und Geschlecht</t>
-  </si>
-  <si>
-    <r>
-      <t>Tabelle 1.3.3: Menschen mit Zuwanderungsgeschichte nach Altersgruppen und Geschlecht</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="9"/>
-        <rFont val="NDSFrutiger 55 Roman"/>
-      </rPr>
-      <t>1,3)</t>
-    </r>
   </si>
   <si>
     <t>Altersgruppe
@@ -114,9 +101,6 @@
     <t>80 und älter</t>
   </si>
   <si>
-    <t xml:space="preserve">1) Hochrechnung anhand der Bevölkerungsfortschreibung auf Basis des Zensus 2011. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe. Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren. </t>
-  </si>
-  <si>
     <t>2) Seit dem Jahr 2018 wird im Mikrozensus der Migrationshintergrund im weiteren Sinne jährlich berichtet. Die in der Tabelle ab dem Jahr 2018 abgebildeten Daten zum Migrationshintergrund entsprechen dem Migrationshintergrund im weiteren Sinne, bis 2017 wird der Migrationshintergrund im engeren Sinne abgebildet. Die Vergleichbarkeit ist dadurch eingeschränkt.</t>
   </si>
   <si>
@@ -141,6 +125,12 @@
     <t>© Landesamt für Statistik Niedersachsen, Hannover 2026,</t>
   </si>
   <si>
+    <t>1) Hochrechnung anhand der Bevölkerungsfortschreibung auf Basis des Zensus 2011. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe. Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren.</t>
+  </si>
+  <si>
+    <t>Tabelle 1.3.3: Menschen mit Zuwanderungsgeschichte nach Altersgruppen und Geschlecht1,3)</t>
+  </si>
+  <si>
     <t>Migration und Teilhabe in Niedersachsen - Integrationsmonitoring 2026</t>
   </si>
 </sst>
@@ -155,7 +145,7 @@
     <numFmt numFmtId="167" formatCode="#\ ##0.0"/>
     <numFmt numFmtId="168" formatCode="\(0.0\)"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,11 +167,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="NDSFrutiger 55 Roman"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
-      <sz val="9"/>
       <name val="NDSFrutiger 55 Roman"/>
     </font>
     <font>
@@ -238,7 +223,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -366,14 +351,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -383,141 +377,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -837,7 +842,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C221C624-F28B-4015-80BC-61E8126DA687}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:I158"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -845,7 +850,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="54" t="s">
         <v>27</v>
       </c>
     </row>
@@ -862,8 +867,8 @@
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>1</v>
+      <c r="B4" s="55" t="s">
+        <v>26</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -873,68 +878,68 @@
       <c r="H4" s="1"/>
     </row>
     <row r="6" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="D6" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+    </row>
+    <row r="7" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="43"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-    </row>
-    <row r="7" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="41"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="H7" s="49"/>
+      <c r="I7" s="50"/>
+    </row>
+    <row r="8" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="43"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="51">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="44"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="48"/>
-    </row>
-    <row r="8" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="41"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="49">
-        <v>1000</v>
-      </c>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="42"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="50"/>
-      <c r="I9" s="51"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="53"/>
     </row>
     <row r="10" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="7">
@@ -962,9 +967,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="16">
         <v>2025</v>
@@ -988,9 +993,9 @@
         <v>36.645777379886603</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="16">
         <v>2025</v>
@@ -1014,9 +1019,9 @@
         <v>38.660671410485882</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="16">
         <v>2025</v>
@@ -1040,9 +1045,9 @@
         <v>39.706851591827373</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="16">
         <v>2025</v>
@@ -1066,9 +1071,9 @@
         <v>39.036101268422946</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="16">
         <v>2025</v>
@@ -1092,9 +1097,9 @@
         <v>33.470328896100433</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="16">
         <v>2025</v>
@@ -1118,9 +1123,9 @@
         <v>24.559166423783154</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" s="16">
         <v>2025</v>
@@ -1144,9 +1149,9 @@
         <v>15.019863138613781</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" s="16">
         <v>2025</v>
@@ -1170,9 +1175,9 @@
         <v>8.8743623067522748</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="18">
         <v>2025</v>
@@ -1198,7 +1203,7 @@
     </row>
     <row r="20" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" s="16">
         <v>2024</v>
@@ -1224,7 +1229,7 @@
     </row>
     <row r="21" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21" s="16">
         <v>2024</v>
@@ -1250,7 +1255,7 @@
     </row>
     <row r="22" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C22" s="16">
         <v>2024</v>
@@ -1276,7 +1281,7 @@
     </row>
     <row r="23" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23" s="16">
         <v>2024</v>
@@ -1302,7 +1307,7 @@
     </row>
     <row r="24" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" s="16">
         <v>2024</v>
@@ -1328,7 +1333,7 @@
     </row>
     <row r="25" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="16">
         <v>2024</v>
@@ -1354,7 +1359,7 @@
     </row>
     <row r="26" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="16">
         <v>2024</v>
@@ -1380,7 +1385,7 @@
     </row>
     <row r="27" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" s="16">
         <v>2024</v>
@@ -1406,7 +1411,7 @@
     </row>
     <row r="28" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="18">
         <v>2024</v>
@@ -1432,7 +1437,7 @@
     </row>
     <row r="29" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="16">
         <v>2023</v>
@@ -1458,7 +1463,7 @@
     </row>
     <row r="30" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" s="16">
         <v>2023</v>
@@ -1484,7 +1489,7 @@
     </row>
     <row r="31" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C31" s="16">
         <v>2023</v>
@@ -1510,7 +1515,7 @@
     </row>
     <row r="32" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" s="16">
         <v>2023</v>
@@ -1536,7 +1541,7 @@
     </row>
     <row r="33" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C33" s="16">
         <v>2023</v>
@@ -1562,7 +1567,7 @@
     </row>
     <row r="34" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34" s="16">
         <v>2023</v>
@@ -1588,7 +1593,7 @@
     </row>
     <row r="35" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C35" s="16">
         <v>2023</v>
@@ -1614,7 +1619,7 @@
     </row>
     <row r="36" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C36" s="16">
         <v>2023</v>
@@ -1640,7 +1645,7 @@
     </row>
     <row r="37" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="18">
         <v>2023</v>
@@ -1666,7 +1671,7 @@
     </row>
     <row r="38" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C38" s="16">
         <v>2022</v>
@@ -1692,7 +1697,7 @@
     </row>
     <row r="39" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C39" s="16">
         <v>2022</v>
@@ -1718,7 +1723,7 @@
     </row>
     <row r="40" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C40" s="16">
         <v>2022</v>
@@ -1744,7 +1749,7 @@
     </row>
     <row r="41" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C41" s="16">
         <v>2022</v>
@@ -1770,7 +1775,7 @@
     </row>
     <row r="42" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C42" s="16">
         <v>2022</v>
@@ -1796,7 +1801,7 @@
     </row>
     <row r="43" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" s="16">
         <v>2022</v>
@@ -1822,7 +1827,7 @@
     </row>
     <row r="44" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C44" s="16">
         <v>2022</v>
@@ -1848,7 +1853,7 @@
     </row>
     <row r="45" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C45" s="16">
         <v>2022</v>
@@ -1874,7 +1879,7 @@
     </row>
     <row r="46" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46" s="18">
         <v>2022</v>
@@ -1900,7 +1905,7 @@
     </row>
     <row r="47" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C47" s="16">
         <v>2021</v>
@@ -1926,7 +1931,7 @@
     </row>
     <row r="48" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C48" s="16">
         <v>2021</v>
@@ -1952,7 +1957,7 @@
     </row>
     <row r="49" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C49" s="16">
         <v>2021</v>
@@ -1978,7 +1983,7 @@
     </row>
     <row r="50" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C50" s="16">
         <v>2021</v>
@@ -2004,7 +2009,7 @@
     </row>
     <row r="51" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C51" s="16">
         <v>2021</v>
@@ -2030,7 +2035,7 @@
     </row>
     <row r="52" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C52" s="16">
         <v>2021</v>
@@ -2056,7 +2061,7 @@
     </row>
     <row r="53" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C53" s="16">
         <v>2021</v>
@@ -2082,7 +2087,7 @@
     </row>
     <row r="54" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C54" s="16">
         <v>2021</v>
@@ -2108,7 +2113,7 @@
     </row>
     <row r="55" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C55" s="22">
         <v>2021</v>
@@ -2134,7 +2139,7 @@
     </row>
     <row r="56" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C56" s="16">
         <v>2019</v>
@@ -2160,7 +2165,7 @@
     </row>
     <row r="57" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C57" s="16">
         <v>2019</v>
@@ -2186,7 +2191,7 @@
     </row>
     <row r="58" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C58" s="16">
         <v>2019</v>
@@ -2212,7 +2217,7 @@
     </row>
     <row r="59" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C59" s="16">
         <v>2019</v>
@@ -2238,7 +2243,7 @@
     </row>
     <row r="60" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C60" s="16">
         <v>2019</v>
@@ -2264,7 +2269,7 @@
     </row>
     <row r="61" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C61" s="16">
         <v>2019</v>
@@ -2290,7 +2295,7 @@
     </row>
     <row r="62" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C62" s="16">
         <v>2019</v>
@@ -2316,7 +2321,7 @@
     </row>
     <row r="63" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C63" s="16">
         <v>2019</v>
@@ -2342,7 +2347,7 @@
     </row>
     <row r="64" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C64" s="22">
         <v>2019</v>
@@ -2368,7 +2373,7 @@
     </row>
     <row r="65" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C65" s="25">
         <v>2018</v>
@@ -2394,7 +2399,7 @@
     </row>
     <row r="66" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C66" s="25">
         <v>2018</v>
@@ -2420,7 +2425,7 @@
     </row>
     <row r="67" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C67" s="25">
         <v>2018</v>
@@ -2446,7 +2451,7 @@
     </row>
     <row r="68" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C68" s="25">
         <v>2018</v>
@@ -2472,7 +2477,7 @@
     </row>
     <row r="69" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C69" s="25">
         <v>2018</v>
@@ -2498,7 +2503,7 @@
     </row>
     <row r="70" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C70" s="25">
         <v>2018</v>
@@ -2524,7 +2529,7 @@
     </row>
     <row r="71" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C71" s="25">
         <v>2018</v>
@@ -2550,7 +2555,7 @@
     </row>
     <row r="72" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C72" s="25">
         <v>2018</v>
@@ -2576,7 +2581,7 @@
     </row>
     <row r="73" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C73" s="27">
         <v>2018</v>
@@ -2602,7 +2607,7 @@
     </row>
     <row r="74" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C74" s="16">
         <v>2017</v>
@@ -2628,7 +2633,7 @@
     </row>
     <row r="75" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C75" s="16">
         <v>2017</v>
@@ -2654,7 +2659,7 @@
     </row>
     <row r="76" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C76" s="16">
         <v>2017</v>
@@ -2680,7 +2685,7 @@
     </row>
     <row r="77" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C77" s="16">
         <v>2017</v>
@@ -2706,7 +2711,7 @@
     </row>
     <row r="78" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C78" s="16">
         <v>2017</v>
@@ -2732,7 +2737,7 @@
     </row>
     <row r="79" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C79" s="16">
         <v>2017</v>
@@ -2758,7 +2763,7 @@
     </row>
     <row r="80" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C80" s="16">
         <v>2017</v>
@@ -2784,7 +2789,7 @@
     </row>
     <row r="81" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C81" s="16">
         <v>2017</v>
@@ -2810,7 +2815,7 @@
     </row>
     <row r="82" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C82" s="22">
         <v>2017</v>
@@ -2836,7 +2841,7 @@
     </row>
     <row r="83" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C83" s="15">
         <v>2016</v>
@@ -2862,7 +2867,7 @@
     </row>
     <row r="84" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C84" s="15">
         <v>2016</v>
@@ -2888,7 +2893,7 @@
     </row>
     <row r="85" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C85" s="15">
         <v>2016</v>
@@ -2914,7 +2919,7 @@
     </row>
     <row r="86" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C86" s="15">
         <v>2016</v>
@@ -2940,7 +2945,7 @@
     </row>
     <row r="87" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C87" s="15">
         <v>2016</v>
@@ -2966,7 +2971,7 @@
     </row>
     <row r="88" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C88" s="15">
         <v>2016</v>
@@ -2992,7 +2997,7 @@
     </row>
     <row r="89" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C89" s="15">
         <v>2016</v>
@@ -3018,7 +3023,7 @@
     </row>
     <row r="90" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C90" s="15">
         <v>2016</v>
@@ -3044,7 +3049,7 @@
     </row>
     <row r="91" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C91" s="18">
         <v>2016</v>
@@ -3070,7 +3075,7 @@
     </row>
     <row r="92" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C92" s="15">
         <v>2015</v>
@@ -3096,7 +3101,7 @@
     </row>
     <row r="93" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C93" s="15">
         <v>2015</v>
@@ -3122,7 +3127,7 @@
     </row>
     <row r="94" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C94" s="15">
         <v>2015</v>
@@ -3148,7 +3153,7 @@
     </row>
     <row r="95" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C95" s="15">
         <v>2015</v>
@@ -3174,7 +3179,7 @@
     </row>
     <row r="96" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C96" s="15">
         <v>2015</v>
@@ -3200,7 +3205,7 @@
     </row>
     <row r="97" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C97" s="15">
         <v>2015</v>
@@ -3226,7 +3231,7 @@
     </row>
     <row r="98" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C98" s="15">
         <v>2015</v>
@@ -3252,7 +3257,7 @@
     </row>
     <row r="99" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C99" s="15">
         <v>2015</v>
@@ -3278,7 +3283,7 @@
     </row>
     <row r="100" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C100" s="18">
         <v>2015</v>
@@ -3304,7 +3309,7 @@
     </row>
     <row r="101" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C101" s="15">
         <v>2014</v>
@@ -3330,7 +3335,7 @@
     </row>
     <row r="102" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C102" s="15">
         <v>2014</v>
@@ -3356,7 +3361,7 @@
     </row>
     <row r="103" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C103" s="15">
         <v>2014</v>
@@ -3382,7 +3387,7 @@
     </row>
     <row r="104" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C104" s="15">
         <v>2014</v>
@@ -3408,7 +3413,7 @@
     </row>
     <row r="105" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C105" s="15">
         <v>2014</v>
@@ -3434,7 +3439,7 @@
     </row>
     <row r="106" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C106" s="15">
         <v>2014</v>
@@ -3460,7 +3465,7 @@
     </row>
     <row r="107" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C107" s="15">
         <v>2014</v>
@@ -3486,7 +3491,7 @@
     </row>
     <row r="108" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C108" s="15">
         <v>2014</v>
@@ -3512,7 +3517,7 @@
     </row>
     <row r="109" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C109" s="18">
         <v>2014</v>
@@ -3538,7 +3543,7 @@
     </row>
     <row r="110" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C110" s="15">
         <v>2013</v>
@@ -3564,7 +3569,7 @@
     </row>
     <row r="111" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C111" s="15">
         <v>2013</v>
@@ -3590,7 +3595,7 @@
     </row>
     <row r="112" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C112" s="15">
         <v>2013</v>
@@ -3616,7 +3621,7 @@
     </row>
     <row r="113" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C113" s="15">
         <v>2013</v>
@@ -3642,7 +3647,7 @@
     </row>
     <row r="114" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C114" s="15">
         <v>2013</v>
@@ -3668,7 +3673,7 @@
     </row>
     <row r="115" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C115" s="15">
         <v>2013</v>
@@ -3694,7 +3699,7 @@
     </row>
     <row r="116" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C116" s="15">
         <v>2013</v>
@@ -3720,7 +3725,7 @@
     </row>
     <row r="117" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C117" s="15">
         <v>2013</v>
@@ -3746,7 +3751,7 @@
     </row>
     <row r="118" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C118" s="18">
         <v>2013</v>
@@ -3772,7 +3777,7 @@
     </row>
     <row r="119" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B119" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C119" s="15">
         <v>2012</v>
@@ -3798,7 +3803,7 @@
     </row>
     <row r="120" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C120" s="15">
         <v>2012</v>
@@ -3824,7 +3829,7 @@
     </row>
     <row r="121" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B121" s="30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C121" s="15">
         <v>2012</v>
@@ -3850,7 +3855,7 @@
     </row>
     <row r="122" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C122" s="15">
         <v>2012</v>
@@ -3876,7 +3881,7 @@
     </row>
     <row r="123" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B123" s="30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C123" s="15">
         <v>2012</v>
@@ -3902,7 +3907,7 @@
     </row>
     <row r="124" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B124" s="30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C124" s="15">
         <v>2012</v>
@@ -3928,7 +3933,7 @@
     </row>
     <row r="125" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B125" s="30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C125" s="15">
         <v>2012</v>
@@ -3954,7 +3959,7 @@
     </row>
     <row r="126" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B126" s="30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C126" s="15">
         <v>2012</v>
@@ -3980,7 +3985,7 @@
     </row>
     <row r="127" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" s="32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C127" s="18">
         <v>2012</v>
@@ -4006,7 +4011,7 @@
     </row>
     <row r="128" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C128" s="15">
         <v>2011</v>
@@ -4032,7 +4037,7 @@
     </row>
     <row r="129" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B129" s="30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C129" s="15">
         <v>2011</v>
@@ -4058,7 +4063,7 @@
     </row>
     <row r="130" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B130" s="30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C130" s="15">
         <v>2011</v>
@@ -4084,7 +4089,7 @@
     </row>
     <row r="131" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B131" s="30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C131" s="15">
         <v>2011</v>
@@ -4110,7 +4115,7 @@
     </row>
     <row r="132" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C132" s="15">
         <v>2011</v>
@@ -4136,7 +4141,7 @@
     </row>
     <row r="133" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C133" s="15">
         <v>2011</v>
@@ -4162,7 +4167,7 @@
     </row>
     <row r="134" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B134" s="30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C134" s="15">
         <v>2011</v>
@@ -4188,7 +4193,7 @@
     </row>
     <row r="135" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C135" s="15">
         <v>2011</v>
@@ -4214,7 +4219,7 @@
     </row>
     <row r="136" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B136" s="32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C136" s="18">
         <v>2011</v>
@@ -4240,7 +4245,7 @@
     </row>
     <row r="137" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B137" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C137" s="15">
         <v>2010</v>
@@ -4266,7 +4271,7 @@
     </row>
     <row r="138" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B138" s="30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C138" s="15">
         <v>2010</v>
@@ -4292,7 +4297,7 @@
     </row>
     <row r="139" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B139" s="30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C139" s="15">
         <v>2010</v>
@@ -4318,7 +4323,7 @@
     </row>
     <row r="140" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B140" s="30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C140" s="15">
         <v>2010</v>
@@ -4344,7 +4349,7 @@
     </row>
     <row r="141" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B141" s="30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C141" s="15">
         <v>2010</v>
@@ -4370,7 +4375,7 @@
     </row>
     <row r="142" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B142" s="30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C142" s="15">
         <v>2010</v>
@@ -4396,7 +4401,7 @@
     </row>
     <row r="143" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B143" s="30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C143" s="15">
         <v>2010</v>
@@ -4422,7 +4427,7 @@
     </row>
     <row r="144" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B144" s="30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C144" s="15">
         <v>2010</v>
@@ -4448,7 +4453,7 @@
     </row>
     <row r="145" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B145" s="32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C145" s="18">
         <v>2010</v>
@@ -4472,56 +4477,41 @@
         <v>16.848005964825198</v>
       </c>
     </row>
-    <row r="147" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="39" t="s">
+    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B146" s="41"/>
+    </row>
+    <row r="147" spans="2:9" s="56" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B147" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C147" s="40"/>
+    </row>
+    <row r="148" spans="2:9" s="56" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B148" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C148" s="40"/>
+    </row>
+    <row r="149" spans="2:9" s="56" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B149" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C147" s="39"/>
-      <c r="D147" s="39"/>
-      <c r="E147" s="39"/>
-      <c r="F147" s="39"/>
-      <c r="G147" s="39"/>
-      <c r="H147" s="39"/>
-      <c r="I147" s="39"/>
-    </row>
-    <row r="148" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B148" s="39" t="s">
+      <c r="C149" s="40"/>
+    </row>
+    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B150" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C148" s="39"/>
-      <c r="D148" s="39"/>
-      <c r="E148" s="39"/>
-      <c r="F148" s="39"/>
-      <c r="G148" s="39"/>
-      <c r="H148" s="39"/>
-      <c r="I148" s="39"/>
-    </row>
-    <row r="149" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="39"/>
-      <c r="C149" s="39"/>
-      <c r="D149" s="39"/>
-      <c r="E149" s="39"/>
-      <c r="F149" s="39"/>
-      <c r="G149" s="39"/>
-      <c r="H149" s="39"/>
-      <c r="I149" s="39"/>
-    </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B150" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="C150" s="39"/>
-      <c r="D150" s="39"/>
-      <c r="E150" s="39"/>
-      <c r="F150" s="39"/>
-      <c r="G150" s="39"/>
-      <c r="H150" s="39"/>
-      <c r="I150" s="39"/>
+      <c r="C150" s="13"/>
+      <c r="D150" s="13"/>
+      <c r="E150" s="13"/>
+      <c r="F150" s="13"/>
+      <c r="G150" s="13"/>
+      <c r="H150" s="13"/>
+      <c r="I150" s="13"/>
     </row>
     <row r="151" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B151" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="B151" s="12"/>
       <c r="C151" s="13"/>
       <c r="D151" s="13"/>
       <c r="E151" s="13"/>
@@ -4531,52 +4521,39 @@
       <c r="I151" s="13"/>
     </row>
     <row r="152" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B152" s="12"/>
-      <c r="C152" s="13"/>
-      <c r="D152" s="13"/>
-      <c r="E152" s="13"/>
-      <c r="F152" s="13"/>
-      <c r="G152" s="13"/>
-      <c r="H152" s="13"/>
-      <c r="I152" s="13"/>
-    </row>
-    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B153" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C153" s="11"/>
-      <c r="D153" s="11"/>
-      <c r="E153" s="11"/>
-      <c r="F153" s="11"/>
-      <c r="G153" s="11"/>
-      <c r="H153" s="11"/>
-      <c r="I153" s="11"/>
+      <c r="B152" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C152" s="11"/>
+      <c r="D152" s="11"/>
+      <c r="E152" s="11"/>
+      <c r="F152" s="11"/>
+      <c r="G152" s="11"/>
+      <c r="H152" s="11"/>
+      <c r="I152" s="11"/>
+    </row>
+    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B154" s="10" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="155" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B155" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="156" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B156" s="10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="157" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B157" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B158" s="14" t="s">
-        <v>25</v>
+      <c r="B157" s="14" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B147:I147"/>
-    <mergeCell ref="B148:I149"/>
-    <mergeCell ref="B150:I150"/>
+  <mergeCells count="6">
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="D6:I6"/>
@@ -4585,9 +4562,10 @@
     <mergeCell ref="G9:I9"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B158" r:id="rId1" xr:uid="{A0EBD9BD-CCB1-41CC-8657-AA4032C938C1}"/>
-    <hyperlink ref="B151" r:id="rId2" xr:uid="{211BF84A-1D3B-42B6-93E4-133DEF5CCC5B}"/>
+    <hyperlink ref="B157" r:id="rId1" xr:uid="{A0EBD9BD-CCB1-41CC-8657-AA4032C938C1}"/>
+    <hyperlink ref="B150" r:id="rId2" xr:uid="{211BF84A-1D3B-42B6-93E4-133DEF5CCC5B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/assets/excel/2026_1-3-3.xlsx
+++ b/assets/excel/2026_1-3-3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BiesterChristophLSN\Desktop\MZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0A6C9B-7126-4BA2-8DA8-376543C74A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128101DE-2F43-470B-8463-5C5EE5586AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{73DE4BD7-C5E9-4923-928A-90D02D9B815D}"/>
+    <workbookView xWindow="20052" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{73DE4BD7-C5E9-4923-928A-90D02D9B815D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -125,13 +125,13 @@
     <t>© Landesamt für Statistik Niedersachsen, Hannover 2026,</t>
   </si>
   <si>
-    <t>1) Hochrechnung anhand der Bevölkerungsfortschreibung auf Basis des Zensus 2011. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe. Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren.</t>
-  </si>
-  <si>
     <t>Tabelle 1.3.3: Menschen mit Zuwanderungsgeschichte nach Altersgruppen und Geschlecht1,3)</t>
   </si>
   <si>
     <t>Migration und Teilhabe in Niedersachsen - Integrationsmonitoring 2026</t>
+  </si>
+  <si>
+    <t>1)  Ab der Veröffentlichung der Endergebnisse 2023 und der Erstergebnisse 2024 werden für die Hochrechnung des Mikrozensus Daten der Bevölkerungsfortschreibung herangezogen, die auf den Eckwerten des Zensus 2022 basieren. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe (auf Basis des Zensus 2011). Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren.</t>
   </si>
 </sst>
 </file>
@@ -396,14 +396,8 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -479,6 +473,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -515,14 +518,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -545,9 +545,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -585,7 +585,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -691,7 +691,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -833,7 +833,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -842,16 +842,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C221C624-F28B-4015-80BC-61E8126DA687}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:I157"/>
+  <dimension ref="A1:N157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38"/>
-      <c r="B1" s="54" t="s">
-        <v>27</v>
+      <c r="A1" s="36"/>
+      <c r="B1" s="40" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -867,8 +867,8 @@
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="55" t="s">
-        <v>26</v>
+      <c r="B4" s="41" t="s">
+        <v>25</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -878,24 +878,24 @@
       <c r="H4" s="1"/>
     </row>
     <row r="6" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
     </row>
     <row r="7" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="43"/>
-      <c r="C7" s="46"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="4" t="s">
         <v>4</v>
       </c>
@@ -905,20 +905,20 @@
       <c r="F7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="49" t="s">
+      <c r="G7" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="49"/>
-      <c r="I7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="51"/>
     </row>
     <row r="8" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="43"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="51">
+      <c r="B8" s="44"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="52">
         <v>1000</v>
       </c>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
       <c r="G8" s="5" t="s">
         <v>4</v>
       </c>
@@ -930,16 +930,16 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="44"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52" t="s">
+      <c r="B9" s="45"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="52"/>
-      <c r="I9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="54"/>
     </row>
     <row r="10" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="7">
@@ -967,3593 +967,3609 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="15" t="s">
+    <row r="11" spans="1:9" s="37" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="14">
         <v>2025</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="15">
         <v>37.409999999999997</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="15">
         <v>36.270000000000003</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="15">
         <v>73.680000000000007</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="15">
         <v>37.67371601208459</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="15">
         <v>35.642688679245282</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="15">
         <v>36.645777379886603</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="15" t="s">
+    <row r="12" spans="1:9" s="37" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="14">
         <v>2025</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="15">
         <v>47.1</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="15">
         <v>41.45</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="15">
         <v>88.56</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="15">
         <v>38.230519480519483</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="15">
         <v>39.151789931047517</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="15">
         <v>38.660671410485882</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="15" t="s">
+    <row r="13" spans="1:9" s="37" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="14">
         <v>2025</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="15">
         <v>140.30000000000001</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="15">
         <v>136.83000000000001</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="15">
         <v>277.13</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="15">
         <v>39.369194937845506</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="15">
         <v>40.059138683139622</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="15">
         <v>39.706851591827373</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="15" t="s">
+    <row r="14" spans="1:9" s="37" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="14">
         <v>2025</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="15">
         <v>82.23</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="15">
         <v>69.8</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="15">
         <v>152.03</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="15">
         <v>39.541257934218123</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="15">
         <v>38.457300275482091</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="15">
         <v>39.036101268422946</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="15" t="s">
+    <row r="15" spans="1:9" s="37" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="14">
         <v>2025</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="15">
         <v>332.87</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="15">
         <v>294.20999999999998</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="15">
         <v>627.08000000000004</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="15">
         <v>34.340922924554583</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="15">
         <v>32.537075744003182</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="15">
         <v>33.470328896100433</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="15" t="s">
+    <row r="16" spans="1:9" s="37" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="14">
         <v>2025</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="15">
         <v>329.36</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="15">
         <v>344.74</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="15">
         <v>674.1</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="15">
         <v>24.343301453088738</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="15">
         <v>24.76900748660028</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="15">
         <v>24.559166423783154</v>
       </c>
     </row>
-    <row r="17" spans="2:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="15" t="s">
+    <row r="17" spans="2:9" s="37" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="14">
         <v>2025</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="15">
         <v>87.5</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="15">
         <v>101.92</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="15">
         <v>189.42</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="15">
         <v>14.715280347112442</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="15">
         <v>15.291593524478253</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="15">
         <v>15.019863138613781</v>
       </c>
     </row>
-    <row r="18" spans="2:9" s="39" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="15" t="s">
+    <row r="18" spans="2:9" s="37" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="14">
         <v>2025</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="15">
         <v>19.3</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="15">
         <v>26.45</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="15">
         <v>45.75</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="15">
         <v>9.2049410979157731</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="15">
         <v>8.6477473353821992</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="15">
         <v>8.8743623067522748</v>
       </c>
     </row>
     <row r="19" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="16">
         <v>2025</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="16">
         <v>1076.08</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="16">
         <v>1051.6600000000001</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="16">
         <v>2127.7399999999998</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="17">
         <v>27.497316911125875</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="17">
         <v>26.297153888085941</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="17">
         <v>26.890732937842966</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="14">
         <v>2024</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="15">
         <v>39.69</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="15">
         <v>40.98</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="15">
         <v>80.680000000000007</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="15">
         <v>36.948426736175755</v>
       </c>
-      <c r="H20" s="17">
+      <c r="H20" s="15">
         <v>39.863813229571981</v>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="15">
         <v>38.378841213966325</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="14">
         <v>2024</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="15">
         <v>44.97</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="15">
         <v>44.5</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="15">
         <v>89.48</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="15">
         <v>38.511604007878738</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="15">
         <v>39.213958406767716</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="15">
         <v>38.86210640608035</v>
       </c>
     </row>
     <row r="22" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="14">
         <v>2024</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="15">
         <v>140.25</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="15">
         <v>136.66</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="15">
         <v>276.91000000000003</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="15">
         <v>39.810951204973172</v>
       </c>
-      <c r="H22" s="17">
+      <c r="H22" s="15">
         <v>41.100751879699246</v>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="15">
         <v>40.437214328480273</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="14">
         <v>2024</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="15">
         <v>76.58</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="15">
         <v>66.540000000000006</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="15">
         <v>143.12</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="15">
         <v>36.713169375329592</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="15">
         <v>36.683389381994601</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="15">
         <v>36.698376881458501</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="14">
         <v>2024</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="15">
         <v>329.53</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="15">
         <v>296.07</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="15">
         <v>625.59</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="15">
         <v>33.802455712043653</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="15">
         <v>32.331582453343231</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="15">
         <v>33.089670420344973</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="14">
         <v>2024</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="15">
         <v>320.42</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="15">
         <v>340.88</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="15">
         <v>661.31</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="15">
         <v>23.527424921066157</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="15">
         <v>24.395794716916317</v>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="15">
         <v>23.967541198685119</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="14">
         <v>2024</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="15">
         <v>86.21</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="15">
         <v>99.55</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="15">
         <v>185.76</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="15">
         <v>14.716626835097301</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="15">
         <v>15.381406344154136</v>
       </c>
-      <c r="I26" s="17">
+      <c r="I26" s="15">
         <v>15.065449060031465</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="14">
         <v>2024</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="15">
         <v>19.149999999999999</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="15">
         <v>26.58</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="15">
         <v>45.73</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="15">
         <v>9.0381347932792142</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="15">
         <v>8.5496477853903308</v>
       </c>
-      <c r="I27" s="17">
+      <c r="I27" s="15">
         <v>8.7476328021883436</v>
       </c>
     </row>
     <row r="28" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="16">
         <v>2024</v>
       </c>
-      <c r="D28" s="18">
+      <c r="D28" s="16">
         <v>1056.82</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="16">
         <v>1051.75</v>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="16">
         <v>2108.5700000000002</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="17">
         <v>26.962995468832919</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="17">
         <v>26.285207307625019</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="17">
         <v>26.620602412376499</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="14">
         <v>2023</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="15">
         <v>42.39</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="15">
         <v>43</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="15">
         <v>85.39</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="15">
         <v>36.224576995385405</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="15">
         <v>40.213223604227061</v>
       </c>
-      <c r="I29" s="17">
+      <c r="I29" s="15">
         <v>38.129046662201389</v>
       </c>
     </row>
     <row r="30" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="14">
         <v>2023</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="15">
         <v>46.24</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="15">
         <v>43.06</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="15">
         <v>89.29</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="15">
         <v>37.948297086581867</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="15">
         <v>37.610271639444498</v>
       </c>
-      <c r="I30" s="17">
+      <c r="I30" s="15">
         <v>37.780316493187783</v>
       </c>
     </row>
     <row r="31" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="16">
+      <c r="C31" s="14">
         <v>2023</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="15">
         <v>129.99</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="15">
         <v>128.88</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="15">
         <v>258.88</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="15">
         <v>37.881392976832295</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="15">
         <v>39.173252279635257</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="15">
         <v>38.515212378189396</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="14">
         <v>2023</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="15">
         <v>70.739999999999995</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="15">
         <v>61.47</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="15">
         <v>132.21</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="15">
         <v>35.490668272125227</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="15">
         <v>34.243217648041892</v>
       </c>
-      <c r="I32" s="17">
+      <c r="I32" s="15">
         <v>34.898637947418436</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="14">
         <v>2023</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="15">
         <v>310.95999999999998</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="15">
         <v>282.10000000000002</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="15">
         <v>593.04999999999995</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="15">
         <v>32.132929639465551</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="15">
         <v>30.76570730590122</v>
       </c>
-      <c r="I33" s="17">
+      <c r="I33" s="15">
         <v>31.467047281486941</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="14">
         <v>2023</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="15">
         <v>299.89999999999998</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="15">
         <v>308.62</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="15">
         <v>608.51</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="15">
         <v>21.849841535827473</v>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="15">
         <v>21.961303360872133</v>
       </c>
-      <c r="I34" s="17">
+      <c r="I34" s="15">
         <v>21.905790449448315</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="14">
         <v>2023</v>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="15">
         <v>75.73</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="15">
         <v>89.29</v>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="15">
         <v>165.02</v>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="15">
         <v>13.121372260244305</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="15">
         <v>14.089374191308741</v>
       </c>
-      <c r="I35" s="17">
+      <c r="I35" s="15">
         <v>13.628105179704017</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="14">
         <v>2023</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="15">
         <v>18.600000000000001</v>
       </c>
-      <c r="E36" s="17">
+      <c r="E36" s="15">
         <v>26.2</v>
       </c>
-      <c r="F36" s="17">
+      <c r="F36" s="15">
         <v>44.8</v>
       </c>
-      <c r="G36" s="17">
+      <c r="G36" s="15">
         <v>8.875739644970416</v>
       </c>
-      <c r="H36" s="17">
+      <c r="H36" s="15">
         <v>8.4467083628860653</v>
       </c>
-      <c r="I36" s="17">
+      <c r="I36" s="15">
         <v>8.6196944626159233</v>
       </c>
     </row>
     <row r="37" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="18">
+      <c r="C37" s="16">
         <v>2023</v>
       </c>
-      <c r="D37" s="18">
+      <c r="D37" s="16">
         <v>994.54</v>
       </c>
-      <c r="E37" s="18">
+      <c r="E37" s="16">
         <v>982.62</v>
       </c>
-      <c r="F37" s="18">
+      <c r="F37" s="16">
         <v>1977.16</v>
       </c>
-      <c r="G37" s="19">
+      <c r="G37" s="17">
         <v>25.446609046295869</v>
       </c>
-      <c r="H37" s="19">
+      <c r="H37" s="17">
         <v>24.589659340301846</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="17">
         <v>25.013378607638014</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="14">
         <v>2022</v>
       </c>
-      <c r="D38" s="20">
+      <c r="D38" s="18">
         <v>44.18</v>
       </c>
-      <c r="E38" s="20">
+      <c r="E38" s="18">
         <v>40.81</v>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="18">
         <v>84.99</v>
       </c>
-      <c r="G38" s="21">
+      <c r="G38" s="19">
         <v>37.520169851380039</v>
       </c>
-      <c r="H38" s="21">
+      <c r="H38" s="19">
         <v>38.012295081967217</v>
       </c>
-      <c r="I38" s="21">
+      <c r="I38" s="19">
         <v>37.75319829424307</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="14">
         <v>2022</v>
       </c>
-      <c r="D39" s="20">
+      <c r="D39" s="18">
         <v>47.45</v>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="18">
         <v>39.54</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="18">
         <v>86.99</v>
       </c>
-      <c r="G39" s="21">
+      <c r="G39" s="19">
         <v>38.389967637540458</v>
       </c>
-      <c r="H39" s="21">
+      <c r="H39" s="19">
         <v>36.42896627971254</v>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="19">
         <v>37.471462416541023</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="14">
         <v>2022</v>
       </c>
-      <c r="D40" s="20">
+      <c r="D40" s="18">
         <v>121.16</v>
       </c>
-      <c r="E40" s="20">
+      <c r="E40" s="18">
         <v>124.07</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="18">
         <v>245.23</v>
       </c>
-      <c r="G40" s="21">
+      <c r="G40" s="19">
         <v>36.766401650785937</v>
       </c>
-      <c r="H40" s="21">
+      <c r="H40" s="19">
         <v>38.348839365746606</v>
       </c>
-      <c r="I40" s="21">
+      <c r="I40" s="19">
         <v>37.550339167317439</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="14">
         <v>2022</v>
       </c>
-      <c r="D41" s="20">
+      <c r="D41" s="18">
         <v>69.290000000000006</v>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="18">
         <v>60.25</v>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="18">
         <v>129.54</v>
       </c>
-      <c r="G41" s="21">
+      <c r="G41" s="19">
         <v>35.062240663900418</v>
       </c>
-      <c r="H41" s="21">
+      <c r="H41" s="19">
         <v>34.147585581500792</v>
       </c>
-      <c r="I41" s="21">
+      <c r="I41" s="19">
         <v>34.630807891782069</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="14">
         <v>2022</v>
       </c>
-      <c r="D42" s="20">
+      <c r="D42" s="18">
         <v>296.08</v>
       </c>
-      <c r="E42" s="20">
+      <c r="E42" s="18">
         <v>265.93</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="18">
         <v>562.02</v>
       </c>
-      <c r="G42" s="21">
+      <c r="G42" s="19">
         <v>30.858060011047534</v>
       </c>
-      <c r="H42" s="21">
+      <c r="H42" s="19">
         <v>29.13471230115255</v>
       </c>
-      <c r="I42" s="21">
+      <c r="I42" s="19">
         <v>30.018427026305243</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="14">
         <v>2022</v>
       </c>
-      <c r="D43" s="20">
+      <c r="D43" s="18">
         <v>295.87</v>
       </c>
-      <c r="E43" s="20">
+      <c r="E43" s="18">
         <v>298.82</v>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="18">
         <v>594.69000000000005</v>
       </c>
-      <c r="G43" s="21">
+      <c r="G43" s="19">
         <v>21.46645480994566</v>
       </c>
-      <c r="H43" s="21">
+      <c r="H43" s="19">
         <v>21.289086155183341</v>
       </c>
-      <c r="I43" s="21">
+      <c r="I43" s="19">
         <v>21.376962673261634</v>
       </c>
     </row>
     <row r="44" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="14">
         <v>2022</v>
       </c>
-      <c r="D44" s="20">
+      <c r="D44" s="18">
         <v>70.41</v>
       </c>
-      <c r="E44" s="20">
+      <c r="E44" s="18">
         <v>82.38</v>
       </c>
-      <c r="F44" s="20">
+      <c r="F44" s="18">
         <v>152.79</v>
       </c>
-      <c r="G44" s="21">
+      <c r="G44" s="19">
         <v>12.435315518977056</v>
       </c>
-      <c r="H44" s="21">
+      <c r="H44" s="19">
         <v>13.148402336642512</v>
       </c>
-      <c r="I44" s="21">
+      <c r="I44" s="19">
         <v>12.809893104171033</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="16">
+      <c r="C45" s="14">
         <v>2022</v>
       </c>
-      <c r="D45" s="20">
+      <c r="D45" s="18">
         <v>20.22</v>
       </c>
-      <c r="E45" s="20">
+      <c r="E45" s="18">
         <v>24.59</v>
       </c>
-      <c r="F45" s="20">
+      <c r="F45" s="18">
         <v>44.81</v>
       </c>
-      <c r="G45" s="21">
+      <c r="G45" s="19">
         <v>9.6936574140658713</v>
       </c>
-      <c r="H45" s="21">
+      <c r="H45" s="19">
         <v>7.9044649458356115</v>
       </c>
-      <c r="I45" s="21">
+      <c r="I45" s="19">
         <v>8.6226139162561584</v>
       </c>
     </row>
     <row r="46" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="16">
         <v>2022</v>
       </c>
-      <c r="D46" s="18">
+      <c r="D46" s="16">
         <v>964.66</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="16">
         <v>936.38</v>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="16">
         <v>1901.04</v>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="17">
         <v>24.855324521398572</v>
       </c>
-      <c r="H46" s="19">
+      <c r="H46" s="17">
         <v>23.586992115670419</v>
       </c>
-      <c r="I46" s="19">
+      <c r="I46" s="17">
         <v>24.213985479556744</v>
       </c>
     </row>
     <row r="47" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C47" s="16">
+      <c r="C47" s="14">
         <v>2021</v>
       </c>
-      <c r="D47" s="17">
+      <c r="D47" s="15">
         <v>42.97</v>
       </c>
-      <c r="E47" s="17">
+      <c r="E47" s="15">
         <v>40.4</v>
       </c>
-      <c r="F47" s="17">
+      <c r="F47" s="15">
         <v>83.37</v>
       </c>
-      <c r="G47" s="17">
+      <c r="G47" s="15">
         <v>36.443049783733358</v>
       </c>
-      <c r="H47" s="17">
+      <c r="H47" s="15">
         <v>38.373860182370819</v>
       </c>
-      <c r="I47" s="17">
+      <c r="I47" s="15">
         <v>37.355497804462765</v>
       </c>
     </row>
     <row r="48" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="16">
+      <c r="C48" s="14">
         <v>2021</v>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="15">
         <v>39.770000000000003</v>
       </c>
-      <c r="E48" s="17">
+      <c r="E48" s="15">
         <v>39.369999999999997</v>
       </c>
-      <c r="F48" s="17">
+      <c r="F48" s="15">
         <v>79.13</v>
       </c>
-      <c r="G48" s="17">
+      <c r="G48" s="15">
         <v>34.962637362637366</v>
       </c>
-      <c r="H48" s="17">
+      <c r="H48" s="15">
         <v>35.612844866576211</v>
       </c>
-      <c r="I48" s="17">
+      <c r="I48" s="15">
         <v>35.278644672313867</v>
       </c>
     </row>
     <row r="49" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="16">
+      <c r="C49" s="14">
         <v>2021</v>
       </c>
-      <c r="D49" s="17">
+      <c r="D49" s="15">
         <v>118.82</v>
       </c>
-      <c r="E49" s="17">
+      <c r="E49" s="15">
         <v>109.86</v>
       </c>
-      <c r="F49" s="17">
+      <c r="F49" s="15">
         <v>228.68</v>
       </c>
-      <c r="G49" s="17">
+      <c r="G49" s="15">
         <v>36.672839506172835</v>
       </c>
-      <c r="H49" s="17">
+      <c r="H49" s="15">
         <v>35.474183861280636</v>
       </c>
-      <c r="I49" s="17">
+      <c r="I49" s="15">
         <v>36.087045716359732</v>
       </c>
     </row>
     <row r="50" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C50" s="16">
+      <c r="C50" s="14">
         <v>2021</v>
       </c>
-      <c r="D50" s="17">
+      <c r="D50" s="15">
         <v>66.05</v>
       </c>
-      <c r="E50" s="17">
+      <c r="E50" s="15">
         <v>55.29</v>
       </c>
-      <c r="F50" s="17">
+      <c r="F50" s="15">
         <v>121.34</v>
       </c>
-      <c r="G50" s="17">
+      <c r="G50" s="15">
         <v>33.102791560166388</v>
       </c>
-      <c r="H50" s="17">
+      <c r="H50" s="15">
         <v>30.397492990268844</v>
       </c>
-      <c r="I50" s="17">
+      <c r="I50" s="15">
         <v>31.812699910859422</v>
       </c>
     </row>
     <row r="51" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C51" s="16">
+      <c r="C51" s="14">
         <v>2021</v>
       </c>
-      <c r="D51" s="17">
+      <c r="D51" s="15">
         <v>282.36</v>
       </c>
-      <c r="E51" s="17">
+      <c r="E51" s="15">
         <v>250.42</v>
       </c>
-      <c r="F51" s="17">
+      <c r="F51" s="15">
         <v>532.78</v>
       </c>
-      <c r="G51" s="17">
+      <c r="G51" s="15">
         <v>29.982161060142715</v>
       </c>
-      <c r="H51" s="17">
+      <c r="H51" s="15">
         <v>28.125070194748307</v>
       </c>
-      <c r="I51" s="17">
+      <c r="I51" s="15">
         <v>29.07965548484286</v>
       </c>
     </row>
     <row r="52" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="16">
+      <c r="C52" s="14">
         <v>2021</v>
       </c>
-      <c r="D52" s="17">
+      <c r="D52" s="15">
         <v>289.12</v>
       </c>
-      <c r="E52" s="17">
+      <c r="E52" s="15">
         <v>282.05</v>
       </c>
-      <c r="F52" s="17">
+      <c r="F52" s="15">
         <v>571.16</v>
       </c>
-      <c r="G52" s="17">
+      <c r="G52" s="15">
         <v>20.84453833010101</v>
       </c>
-      <c r="H52" s="17">
+      <c r="H52" s="15">
         <v>20.190270301225517</v>
       </c>
-      <c r="I52" s="17">
+      <c r="I52" s="15">
         <v>20.515878289792706</v>
       </c>
     </row>
     <row r="53" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="15" t="s">
+      <c r="B53" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="14">
         <v>2021</v>
       </c>
-      <c r="D53" s="17">
+      <c r="D53" s="15">
         <v>70.069999999999993</v>
       </c>
-      <c r="E53" s="17">
+      <c r="E53" s="15">
         <v>76.36</v>
       </c>
-      <c r="F53" s="17">
+      <c r="F53" s="15">
         <v>146.43</v>
       </c>
-      <c r="G53" s="17">
+      <c r="G53" s="15">
         <v>12.622950819672131</v>
       </c>
-      <c r="H53" s="17">
+      <c r="H53" s="15">
         <v>12.54497363189801</v>
       </c>
-      <c r="I53" s="17">
+      <c r="I53" s="15">
         <v>12.582275000429636</v>
       </c>
     </row>
     <row r="54" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="14">
         <v>2021</v>
       </c>
-      <c r="D54" s="17">
+      <c r="D54" s="15">
         <v>19.34</v>
       </c>
-      <c r="E54" s="17">
+      <c r="E54" s="15">
         <v>24.44</v>
       </c>
-      <c r="F54" s="17">
+      <c r="F54" s="15">
         <v>43.78</v>
       </c>
-      <c r="G54" s="17">
+      <c r="G54" s="15">
         <v>9.5242785383630455</v>
       </c>
-      <c r="H54" s="17">
+      <c r="H54" s="15">
         <v>7.985101447381318</v>
       </c>
-      <c r="I54" s="17">
+      <c r="I54" s="15">
         <v>8.5988136858231528</v>
       </c>
     </row>
     <row r="55" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="18" t="s">
+      <c r="B55" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C55" s="22">
+      <c r="C55" s="20">
         <v>2021</v>
       </c>
-      <c r="D55" s="23">
+      <c r="D55" s="21">
         <v>928.49</v>
       </c>
-      <c r="E55" s="23">
+      <c r="E55" s="21">
         <v>878.18</v>
       </c>
-      <c r="F55" s="23">
+      <c r="F55" s="21">
         <v>1806.68</v>
       </c>
-      <c r="G55" s="24">
+      <c r="G55" s="22">
         <v>24.166022492731894</v>
       </c>
-      <c r="H55" s="24">
+      <c r="H55" s="22">
         <v>22.462661561167511</v>
       </c>
-      <c r="I55" s="24">
+      <c r="I55" s="22">
         <v>23.307067923690987</v>
       </c>
     </row>
     <row r="56" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="15" t="s">
+      <c r="B56" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="16">
+      <c r="C56" s="14">
         <v>2019</v>
       </c>
-      <c r="D56" s="20">
+      <c r="D56" s="18">
         <v>41.174480000000003</v>
       </c>
-      <c r="E56" s="20">
+      <c r="E56" s="18">
         <v>42.138500000000001</v>
       </c>
-      <c r="F56" s="20">
+      <c r="F56" s="18">
         <v>83.31298000000001</v>
       </c>
-      <c r="G56" s="21">
+      <c r="G56" s="19">
         <v>38.112417825858813</v>
       </c>
-      <c r="H56" s="21">
+      <c r="H56" s="19">
         <v>39.665047156868418</v>
       </c>
-      <c r="I56" s="21">
+      <c r="I56" s="19">
         <v>38.882216626171058</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="16">
+      <c r="C57" s="14">
         <v>2019</v>
       </c>
-      <c r="D57" s="20">
+      <c r="D57" s="18">
         <v>38.463839999999998</v>
       </c>
-      <c r="E57" s="20">
+      <c r="E57" s="18">
         <v>37.170290000000001</v>
       </c>
-      <c r="F57" s="20">
+      <c r="F57" s="18">
         <v>75.634129999999999</v>
       </c>
-      <c r="G57" s="21">
+      <c r="G57" s="19">
         <v>34.38202030249581</v>
       </c>
-      <c r="H57" s="21">
+      <c r="H57" s="19">
         <v>34.334611595623272</v>
       </c>
-      <c r="I57" s="21">
+      <c r="I57" s="19">
         <v>34.358705008760474</v>
       </c>
     </row>
     <row r="58" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C58" s="16">
+      <c r="C58" s="14">
         <v>2019</v>
       </c>
-      <c r="D58" s="20">
+      <c r="D58" s="18">
         <v>117.68767999999999</v>
       </c>
-      <c r="E58" s="20">
+      <c r="E58" s="18">
         <v>109.78658999999999</v>
       </c>
-      <c r="F58" s="20">
+      <c r="F58" s="18">
         <v>227.47426999999999</v>
       </c>
-      <c r="G58" s="21">
+      <c r="G58" s="19">
         <v>35.27162141466296</v>
       </c>
-      <c r="H58" s="21">
+      <c r="H58" s="19">
         <v>35.339458450318389</v>
       </c>
-      <c r="I58" s="21">
+      <c r="I58" s="19">
         <v>35.304328713370019</v>
       </c>
     </row>
     <row r="59" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C59" s="16">
+      <c r="C59" s="14">
         <v>2019</v>
       </c>
-      <c r="D59" s="20">
+      <c r="D59" s="18">
         <v>62.029480000000007</v>
       </c>
-      <c r="E59" s="20">
+      <c r="E59" s="18">
         <v>55.115300000000005</v>
       </c>
-      <c r="F59" s="20">
+      <c r="F59" s="18">
         <v>117.14478000000001</v>
       </c>
-      <c r="G59" s="21">
+      <c r="G59" s="19">
         <v>30.982686861307634</v>
       </c>
-      <c r="H59" s="21">
+      <c r="H59" s="19">
         <v>28.057745646860514</v>
       </c>
-      <c r="I59" s="21">
+      <c r="I59" s="19">
         <v>29.534122886334696</v>
       </c>
     </row>
     <row r="60" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="15" t="s">
+      <c r="B60" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C60" s="16">
+      <c r="C60" s="14">
         <v>2019</v>
       </c>
-      <c r="D60" s="20">
+      <c r="D60" s="18">
         <v>293.56018999999998</v>
       </c>
-      <c r="E60" s="20">
+      <c r="E60" s="18">
         <v>256.22624000000002</v>
       </c>
-      <c r="F60" s="20">
+      <c r="F60" s="18">
         <v>549.78643</v>
       </c>
-      <c r="G60" s="21">
+      <c r="G60" s="19">
         <v>30.19194861390444</v>
       </c>
-      <c r="H60" s="21">
+      <c r="H60" s="19">
         <v>28.578611849207867</v>
       </c>
-      <c r="I60" s="21">
+      <c r="I60" s="19">
         <v>29.417974813418386</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C61" s="16">
+      <c r="C61" s="14">
         <v>2019</v>
       </c>
-      <c r="D61" s="20">
+      <c r="D61" s="18">
         <v>272.82486999999998</v>
       </c>
-      <c r="E61" s="20">
+      <c r="E61" s="18">
         <v>260.36651000000001</v>
       </c>
-      <c r="F61" s="20">
+      <c r="F61" s="18">
         <v>533.19137999999998</v>
       </c>
-      <c r="G61" s="21">
+      <c r="G61" s="19">
         <v>19.253290661166183</v>
       </c>
-      <c r="H61" s="21">
+      <c r="H61" s="19">
         <v>18.187697938027938</v>
       </c>
-      <c r="I61" s="21">
+      <c r="I61" s="19">
         <v>18.717777923160018</v>
       </c>
     </row>
     <row r="62" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="16">
+      <c r="C62" s="14">
         <v>2019</v>
       </c>
-      <c r="D62" s="20">
+      <c r="D62" s="18">
         <v>63.221890000000002</v>
       </c>
-      <c r="E62" s="20">
+      <c r="E62" s="18">
         <v>69.251609999999999</v>
       </c>
-      <c r="F62" s="20">
+      <c r="F62" s="18">
         <v>132.4735</v>
       </c>
-      <c r="G62" s="21">
+      <c r="G62" s="19">
         <v>11.194301339600161</v>
       </c>
-      <c r="H62" s="21">
+      <c r="H62" s="19">
         <v>11.079403333685359</v>
       </c>
-      <c r="I62" s="21">
+      <c r="I62" s="19">
         <v>11.133941798480878</v>
       </c>
     </row>
     <row r="63" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C63" s="16">
+      <c r="C63" s="14">
         <v>2019</v>
       </c>
-      <c r="D63" s="20">
+      <c r="D63" s="18">
         <v>12.31427</v>
       </c>
-      <c r="E63" s="20">
+      <c r="E63" s="18">
         <v>19.459959999999999</v>
       </c>
-      <c r="F63" s="20">
+      <c r="F63" s="18">
         <v>31.774229999999999</v>
       </c>
-      <c r="G63" s="21">
+      <c r="G63" s="19">
         <v>6.7183272921179125</v>
       </c>
-      <c r="H63" s="21">
+      <c r="H63" s="19">
         <v>6.9848187559638921</v>
       </c>
-      <c r="I63" s="21">
+      <c r="I63" s="19">
         <v>6.8790675434502386</v>
       </c>
     </row>
     <row r="64" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="18" t="s">
+      <c r="B64" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C64" s="22">
+      <c r="C64" s="20">
         <v>2019</v>
       </c>
-      <c r="D64" s="23">
+      <c r="D64" s="21">
         <v>901.27668999999992</v>
       </c>
-      <c r="E64" s="23">
+      <c r="E64" s="21">
         <v>849.51499000000001</v>
       </c>
-      <c r="F64" s="23">
+      <c r="F64" s="21">
         <v>1750.7916799999998</v>
       </c>
-      <c r="G64" s="24">
+      <c r="G64" s="22">
         <v>23.162045742160423</v>
       </c>
-      <c r="H64" s="24">
+      <c r="H64" s="22">
         <v>21.488407719555159</v>
       </c>
-      <c r="I64" s="24">
+      <c r="I64" s="22">
         <v>22.318593133632049</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C65" s="25">
+      <c r="C65" s="23">
         <v>2018</v>
       </c>
-      <c r="D65" s="26">
+      <c r="D65" s="24">
         <v>39.061250000000001</v>
       </c>
-      <c r="E65" s="26">
+      <c r="E65" s="24">
         <v>37.879100000000001</v>
       </c>
-      <c r="F65" s="26">
+      <c r="F65" s="24">
         <v>76.940349999999995</v>
       </c>
-      <c r="G65" s="26">
+      <c r="G65" s="24">
         <v>36.676048837112575</v>
       </c>
-      <c r="H65" s="26">
+      <c r="H65" s="24">
         <v>37.648903310488677</v>
       </c>
-      <c r="I65" s="26">
+      <c r="I65" s="24">
         <v>37.148638200078935</v>
       </c>
     </row>
     <row r="66" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C66" s="25">
+      <c r="C66" s="23">
         <v>2018</v>
       </c>
-      <c r="D66" s="26">
+      <c r="D66" s="24">
         <v>36.041019999999996</v>
       </c>
-      <c r="E66" s="26">
+      <c r="E66" s="24">
         <v>38.648029999999999</v>
       </c>
-      <c r="F66" s="26">
+      <c r="F66" s="24">
         <v>74.689049999999995</v>
       </c>
-      <c r="G66" s="26">
+      <c r="G66" s="24">
         <v>36.666957972858874</v>
       </c>
-      <c r="H66" s="26">
+      <c r="H66" s="24">
         <v>37.641928993476562</v>
       </c>
-      <c r="I66" s="26">
+      <c r="I66" s="24">
         <v>37.165067894909235</v>
       </c>
     </row>
     <row r="67" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C67" s="25">
+      <c r="C67" s="23">
         <v>2018</v>
       </c>
-      <c r="D67" s="26">
+      <c r="D67" s="24">
         <v>116.42134</v>
       </c>
-      <c r="E67" s="26">
+      <c r="E67" s="24">
         <v>103.20057000000001</v>
       </c>
-      <c r="F67" s="26">
+      <c r="F67" s="24">
         <v>219.62191000000001</v>
       </c>
-      <c r="G67" s="26">
+      <c r="G67" s="24">
         <v>35.100307879400802</v>
       </c>
-      <c r="H67" s="26">
+      <c r="H67" s="24">
         <v>33.882148884628478</v>
       </c>
-      <c r="I67" s="26">
+      <c r="I67" s="24">
         <v>34.517165523803016</v>
       </c>
     </row>
     <row r="68" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C68" s="25">
+      <c r="C68" s="23">
         <v>2018</v>
       </c>
-      <c r="D68" s="26">
+      <c r="D68" s="24">
         <v>59.581510000000002</v>
       </c>
-      <c r="E68" s="26">
+      <c r="E68" s="24">
         <v>56.277790000000003</v>
       </c>
-      <c r="F68" s="26">
+      <c r="F68" s="24">
         <v>115.8593</v>
       </c>
-      <c r="G68" s="26">
+      <c r="G68" s="24">
         <v>28.458009499136445</v>
       </c>
-      <c r="H68" s="26">
+      <c r="H68" s="24">
         <v>28.73685140401474</v>
       </c>
-      <c r="I68" s="26">
+      <c r="I68" s="24">
         <v>28.592775801273827</v>
       </c>
     </row>
     <row r="69" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="15" t="s">
+      <c r="B69" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C69" s="25">
+      <c r="C69" s="23">
         <v>2018</v>
       </c>
-      <c r="D69" s="26">
+      <c r="D69" s="24">
         <v>299.2321</v>
       </c>
-      <c r="E69" s="26">
+      <c r="E69" s="24">
         <v>252.66542000000001</v>
       </c>
-      <c r="F69" s="26">
+      <c r="F69" s="24">
         <v>551.89751999999999</v>
       </c>
-      <c r="G69" s="26">
+      <c r="G69" s="24">
         <v>30.718905844252635</v>
       </c>
-      <c r="H69" s="26">
+      <c r="H69" s="24">
         <v>28.194515038018654</v>
       </c>
-      <c r="I69" s="26">
+      <c r="I69" s="24">
         <v>29.509315096412671</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C70" s="25">
+      <c r="C70" s="23">
         <v>2018</v>
       </c>
-      <c r="D70" s="26">
+      <c r="D70" s="24">
         <v>265.28469999999999</v>
       </c>
-      <c r="E70" s="26">
+      <c r="E70" s="24">
         <v>259.90300999999999</v>
       </c>
-      <c r="F70" s="26">
+      <c r="F70" s="24">
         <v>525.18770999999992</v>
       </c>
-      <c r="G70" s="26">
+      <c r="G70" s="24">
         <v>18.787014074855804</v>
       </c>
-      <c r="H70" s="26">
+      <c r="H70" s="24">
         <v>18.302180399622742</v>
       </c>
-      <c r="I70" s="26">
+      <c r="I70" s="24">
         <v>18.543912401309878</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="15" t="s">
+      <c r="B71" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C71" s="25">
+      <c r="C71" s="23">
         <v>2018</v>
       </c>
-      <c r="D71" s="26">
+      <c r="D71" s="24">
         <v>64.191199999999995</v>
       </c>
-      <c r="E71" s="26">
+      <c r="E71" s="24">
         <v>66.431100000000001</v>
       </c>
-      <c r="F71" s="26">
+      <c r="F71" s="24">
         <v>130.6223</v>
       </c>
-      <c r="G71" s="26">
+      <c r="G71" s="24">
         <v>10.972840445540617</v>
       </c>
-      <c r="H71" s="26">
+      <c r="H71" s="24">
         <v>10.293760273155275</v>
       </c>
-      <c r="I71" s="26">
+      <c r="I71" s="24">
         <v>10.616644959496814</v>
       </c>
     </row>
     <row r="72" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="15" t="s">
+      <c r="B72" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C72" s="25">
+      <c r="C72" s="23">
         <v>2018</v>
       </c>
-      <c r="D72" s="26">
+      <c r="D72" s="24">
         <v>10.583440000000001</v>
       </c>
-      <c r="E72" s="26">
+      <c r="E72" s="24">
         <v>20.704909999999998</v>
       </c>
-      <c r="F72" s="26">
+      <c r="F72" s="24">
         <v>31.288350000000001</v>
       </c>
-      <c r="G72" s="26">
+      <c r="G72" s="24">
         <v>6.1906004469003042</v>
       </c>
-      <c r="H72" s="26">
+      <c r="H72" s="24">
         <v>7.6605783334445769</v>
       </c>
-      <c r="I72" s="26">
+      <c r="I72" s="24">
         <v>7.0910286799076374</v>
       </c>
     </row>
     <row r="73" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="18" t="s">
+      <c r="B73" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C73" s="27">
+      <c r="C73" s="25">
         <v>2018</v>
       </c>
-      <c r="D73" s="28">
+      <c r="D73" s="26">
         <v>890.39656000000002</v>
       </c>
-      <c r="E73" s="28">
+      <c r="E73" s="26">
         <v>835.70993999999996</v>
       </c>
-      <c r="F73" s="29">
+      <c r="F73" s="27">
         <v>1726.1064999999999</v>
       </c>
-      <c r="G73" s="28">
+      <c r="G73" s="26">
         <v>22.901341234937014</v>
       </c>
-      <c r="H73" s="28">
+      <c r="H73" s="26">
         <v>21.23485221499984</v>
       </c>
-      <c r="I73" s="28">
+      <c r="I73" s="26">
         <v>22.063028024296166</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="30" t="s">
+      <c r="B74" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C74" s="16">
+      <c r="C74" s="14">
         <v>2017</v>
       </c>
-      <c r="D74" s="31">
+      <c r="D74" s="29">
         <v>41.215350000000001</v>
       </c>
-      <c r="E74" s="31">
+      <c r="E74" s="29">
         <v>39.082809999999995</v>
       </c>
-      <c r="F74" s="31">
+      <c r="F74" s="29">
         <v>80.298159999999996</v>
       </c>
-      <c r="G74" s="17">
+      <c r="G74" s="15">
         <v>38.148493427296707</v>
       </c>
-      <c r="H74" s="17">
+      <c r="H74" s="15">
         <v>36.758762943999677</v>
       </c>
-      <c r="I74" s="17">
+      <c r="I74" s="15">
         <v>37.459193384788115</v>
       </c>
     </row>
     <row r="75" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="30" t="s">
+      <c r="B75" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C75" s="16">
+      <c r="C75" s="14">
         <v>2017</v>
       </c>
-      <c r="D75" s="31">
+      <c r="D75" s="29">
         <v>36.881239999999998</v>
       </c>
-      <c r="E75" s="31">
+      <c r="E75" s="29">
         <v>36.524320000000003</v>
       </c>
-      <c r="F75" s="31">
+      <c r="F75" s="29">
         <v>73.405560000000008</v>
       </c>
-      <c r="G75" s="17">
+      <c r="G75" s="15">
         <v>36.340386034646357</v>
       </c>
-      <c r="H75" s="17">
+      <c r="H75" s="15">
         <v>36.207400246383429</v>
       </c>
-      <c r="I75" s="17">
+      <c r="I75" s="15">
         <v>36.274094564145656</v>
       </c>
     </row>
     <row r="76" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="30" t="s">
+      <c r="B76" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C76" s="16">
+      <c r="C76" s="14">
         <v>2017</v>
       </c>
-      <c r="D76" s="31">
+      <c r="D76" s="29">
         <v>118.75583999999999</v>
       </c>
-      <c r="E76" s="31">
+      <c r="E76" s="29">
         <v>104.13961</v>
       </c>
-      <c r="F76" s="31">
+      <c r="F76" s="29">
         <v>222.89544999999998</v>
       </c>
-      <c r="G76" s="17">
+      <c r="G76" s="15">
         <v>34.759146328078003</v>
       </c>
-      <c r="H76" s="17">
+      <c r="H76" s="15">
         <v>33.222882414546305</v>
       </c>
-      <c r="I76" s="17">
+      <c r="I76" s="15">
         <v>34.024074821643204</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="30" t="s">
+      <c r="B77" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C77" s="16">
+      <c r="C77" s="14">
         <v>2017</v>
       </c>
-      <c r="D77" s="31">
+      <c r="D77" s="29">
         <v>66.812559999999991</v>
       </c>
-      <c r="E77" s="31">
+      <c r="E77" s="29">
         <v>55.912330000000004</v>
       </c>
-      <c r="F77" s="31">
+      <c r="F77" s="29">
         <v>122.72488999999999</v>
       </c>
-      <c r="G77" s="17">
+      <c r="G77" s="15">
         <v>30.069566907263489</v>
       </c>
-      <c r="H77" s="17">
+      <c r="H77" s="15">
         <v>27.907311855231825</v>
       </c>
-      <c r="I77" s="17">
+      <c r="I77" s="15">
         <v>29.044327754261456</v>
       </c>
     </row>
     <row r="78" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="30" t="s">
+      <c r="B78" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C78" s="16">
+      <c r="C78" s="14">
         <v>2017</v>
       </c>
-      <c r="D78" s="31">
+      <c r="D78" s="29">
         <v>303.93865</v>
       </c>
-      <c r="E78" s="31">
+      <c r="E78" s="29">
         <v>255.05915999999999</v>
       </c>
-      <c r="F78" s="31">
+      <c r="F78" s="29">
         <v>558.99780999999996</v>
       </c>
-      <c r="G78" s="17">
+      <c r="G78" s="15">
         <v>31.227626706986932</v>
       </c>
-      <c r="H78" s="17">
+      <c r="H78" s="15">
         <v>28.424547705683111</v>
       </c>
-      <c r="I78" s="17">
+      <c r="I78" s="15">
         <v>29.883014649245755</v>
       </c>
     </row>
     <row r="79" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="30" t="s">
+      <c r="B79" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C79" s="16">
+      <c r="C79" s="14">
         <v>2017</v>
       </c>
-      <c r="D79" s="31">
+      <c r="D79" s="29">
         <v>262.8365</v>
       </c>
-      <c r="E79" s="31">
+      <c r="E79" s="29">
         <v>258.38357000000002</v>
       </c>
-      <c r="F79" s="31">
+      <c r="F79" s="29">
         <v>521.22007000000008</v>
       </c>
-      <c r="G79" s="17">
+      <c r="G79" s="15">
         <v>18.359180268030141</v>
       </c>
-      <c r="H79" s="17">
+      <c r="H79" s="15">
         <v>18.085951896316445</v>
       </c>
-      <c r="I79" s="17">
+      <c r="I79" s="15">
         <v>18.222709031220862</v>
       </c>
     </row>
     <row r="80" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="30" t="s">
+      <c r="B80" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C80" s="16">
+      <c r="C80" s="14">
         <v>2017</v>
       </c>
-      <c r="D80" s="31">
+      <c r="D80" s="29">
         <v>59.673269999999995</v>
       </c>
-      <c r="E80" s="31">
+      <c r="E80" s="29">
         <v>62.01549</v>
       </c>
-      <c r="F80" s="31">
+      <c r="F80" s="29">
         <v>121.68876</v>
       </c>
-      <c r="G80" s="17">
+      <c r="G80" s="15">
         <v>10.462021340757904</v>
       </c>
-      <c r="H80" s="17">
+      <c r="H80" s="15">
         <v>9.7827886306832195</v>
       </c>
-      <c r="I80" s="17">
+      <c r="I80" s="15">
         <v>10.104485295449265</v>
       </c>
     </row>
     <row r="81" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="30" t="s">
+      <c r="B81" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C81" s="16">
+      <c r="C81" s="14">
         <v>2017</v>
       </c>
-      <c r="D81" s="31">
+      <c r="D81" s="29">
         <v>13.257950000000001</v>
       </c>
-      <c r="E81" s="31">
+      <c r="E81" s="29">
         <v>18.926380000000002</v>
       </c>
-      <c r="F81" s="31">
+      <c r="F81" s="29">
         <v>32.184330000000003</v>
       </c>
-      <c r="G81" s="17">
+      <c r="G81" s="15">
         <v>8.1864686758025158</v>
       </c>
-      <c r="H81" s="17">
+      <c r="H81" s="15">
         <v>7.2124473534496607</v>
       </c>
-      <c r="I81" s="17">
+      <c r="I81" s="15">
         <v>7.5841635221640464</v>
       </c>
     </row>
     <row r="82" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="32" t="s">
+      <c r="B82" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C82" s="22">
+      <c r="C82" s="20">
         <v>2017</v>
       </c>
-      <c r="D82" s="33">
+      <c r="D82" s="31">
         <v>903.37135999999998</v>
       </c>
-      <c r="E82" s="33">
+      <c r="E82" s="31">
         <v>830.04367000000002</v>
       </c>
-      <c r="F82" s="33">
+      <c r="F82" s="31">
         <v>1733.4150300000001</v>
       </c>
-      <c r="G82" s="34">
+      <c r="G82" s="32">
         <v>23.100347968141332</v>
       </c>
-      <c r="H82" s="34">
+      <c r="H82" s="32">
         <v>21.049441801976815</v>
       </c>
-      <c r="I82" s="34">
+      <c r="I82" s="32">
         <v>22.070629931060427</v>
       </c>
     </row>
     <row r="83" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="30" t="s">
+      <c r="B83" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C83" s="15">
+      <c r="C83" s="13">
         <v>2016</v>
       </c>
-      <c r="D83" s="35">
+      <c r="D83" s="33">
         <v>39.462350000000001</v>
       </c>
-      <c r="E83" s="35">
+      <c r="E83" s="33">
         <v>36.863129999999998</v>
       </c>
-      <c r="F83" s="35">
+      <c r="F83" s="33">
         <v>76.325479999999999</v>
       </c>
-      <c r="G83" s="17">
+      <c r="G83" s="15">
         <v>36.588882370781292</v>
       </c>
-      <c r="H83" s="17">
+      <c r="H83" s="15">
         <v>35.99790593176759</v>
       </c>
-      <c r="I83" s="17">
+      <c r="I83" s="15">
         <v>36.301053192396559</v>
       </c>
     </row>
     <row r="84" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="30" t="s">
+      <c r="B84" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C84" s="15">
+      <c r="C84" s="13">
         <v>2016</v>
       </c>
-      <c r="D84" s="35">
+      <c r="D84" s="33">
         <v>39.420120000000004</v>
       </c>
-      <c r="E84" s="35">
+      <c r="E84" s="33">
         <v>31.442430000000002</v>
       </c>
-      <c r="F84" s="35">
+      <c r="F84" s="33">
         <v>70.862549999999999</v>
       </c>
-      <c r="G84" s="17">
+      <c r="G84" s="15">
         <v>36.83301678401277</v>
       </c>
-      <c r="H84" s="17">
+      <c r="H84" s="15">
         <v>32.576293502153355</v>
       </c>
-      <c r="I84" s="17">
+      <c r="I84" s="15">
         <v>34.814496163787908</v>
       </c>
     </row>
     <row r="85" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="30" t="s">
+      <c r="B85" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C85" s="15">
+      <c r="C85" s="13">
         <v>2016</v>
       </c>
-      <c r="D85" s="35">
+      <c r="D85" s="33">
         <v>107.32152000000001</v>
       </c>
-      <c r="E85" s="35">
+      <c r="E85" s="33">
         <v>95.100020000000001</v>
       </c>
-      <c r="F85" s="35">
+      <c r="F85" s="33">
         <v>202.42153999999999</v>
       </c>
-      <c r="G85" s="17">
+      <c r="G85" s="15">
         <v>32.185052192307225</v>
       </c>
-      <c r="H85" s="17">
+      <c r="H85" s="15">
         <v>29.835138463405364</v>
       </c>
-      <c r="I85" s="17">
+      <c r="I85" s="15">
         <v>31.036577145124888</v>
       </c>
     </row>
     <row r="86" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="30" t="s">
+      <c r="B86" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C86" s="15">
+      <c r="C86" s="13">
         <v>2016</v>
       </c>
-      <c r="D86" s="35">
+      <c r="D86" s="33">
         <v>59.288710000000002</v>
       </c>
-      <c r="E86" s="35">
+      <c r="E86" s="33">
         <v>46.485169999999997</v>
       </c>
-      <c r="F86" s="35">
+      <c r="F86" s="33">
         <v>105.77387999999999</v>
       </c>
-      <c r="G86" s="17">
+      <c r="G86" s="15">
         <v>26.473299763440806</v>
       </c>
-      <c r="H86" s="17">
+      <c r="H86" s="15">
         <v>22.517031091505519</v>
       </c>
-      <c r="I86" s="17">
+      <c r="I86" s="15">
         <v>24.575651661873</v>
       </c>
     </row>
     <row r="87" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="30" t="s">
+      <c r="B87" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C87" s="15">
+      <c r="C87" s="13">
         <v>2016</v>
       </c>
-      <c r="D87" s="35">
+      <c r="D87" s="33">
         <v>256.40228999999999</v>
       </c>
-      <c r="E87" s="35">
+      <c r="E87" s="33">
         <v>222.21595000000002</v>
       </c>
-      <c r="F87" s="35">
+      <c r="F87" s="33">
         <v>478.61824000000001</v>
       </c>
-      <c r="G87" s="17">
+      <c r="G87" s="15">
         <v>26.67141387241286</v>
       </c>
-      <c r="H87" s="17">
+      <c r="H87" s="15">
         <v>24.97057459348418</v>
       </c>
-      <c r="I87" s="17">
+      <c r="I87" s="15">
         <v>25.853805735846329</v>
       </c>
     </row>
     <row r="88" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="30" t="s">
+      <c r="B88" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C88" s="15">
+      <c r="C88" s="13">
         <v>2016</v>
       </c>
-      <c r="D88" s="35">
+      <c r="D88" s="33">
         <v>241.36802</v>
       </c>
-      <c r="E88" s="35">
+      <c r="E88" s="33">
         <v>232.29143999999999</v>
       </c>
-      <c r="F88" s="35">
+      <c r="F88" s="33">
         <v>473.65945999999997</v>
       </c>
-      <c r="G88" s="17">
+      <c r="G88" s="15">
         <v>16.615843261135019</v>
       </c>
-      <c r="H88" s="17">
+      <c r="H88" s="15">
         <v>15.990717304684345</v>
       </c>
-      <c r="I88" s="17">
+      <c r="I88" s="15">
         <v>16.303277433019023</v>
       </c>
     </row>
     <row r="89" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="30" t="s">
+      <c r="B89" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C89" s="15">
+      <c r="C89" s="13">
         <v>2016</v>
       </c>
-      <c r="D89" s="35">
+      <c r="D89" s="33">
         <v>55.127900000000004</v>
       </c>
-      <c r="E89" s="35">
+      <c r="E89" s="33">
         <v>62.81429</v>
       </c>
-      <c r="F89" s="35">
+      <c r="F89" s="33">
         <v>117.94219000000001</v>
       </c>
-      <c r="G89" s="17">
+      <c r="G89" s="15">
         <v>9.477095559253744</v>
       </c>
-      <c r="H89" s="17">
+      <c r="H89" s="15">
         <v>9.4750304670585894</v>
       </c>
-      <c r="I89" s="17">
+      <c r="I89" s="15">
         <v>9.4759956092422986</v>
       </c>
     </row>
     <row r="90" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="30" t="s">
+      <c r="B90" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C90" s="15">
+      <c r="C90" s="13">
         <v>2016</v>
       </c>
-      <c r="D90" s="35">
+      <c r="D90" s="33">
         <v>13.007280000000002</v>
       </c>
-      <c r="E90" s="35">
+      <c r="E90" s="33">
         <v>18.565349999999999</v>
       </c>
-      <c r="F90" s="35">
+      <c r="F90" s="33">
         <v>31.57263</v>
       </c>
-      <c r="G90" s="17">
+      <c r="G90" s="15">
         <v>7.9194436940404902</v>
       </c>
-      <c r="H90" s="17">
+      <c r="H90" s="15">
         <v>6.401586998151247</v>
       </c>
-      <c r="I90" s="17">
+      <c r="I90" s="15">
         <v>6.9503962023222332</v>
       </c>
     </row>
     <row r="91" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="32" t="s">
+      <c r="B91" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C91" s="18">
+      <c r="C91" s="16">
         <v>2016</v>
       </c>
-      <c r="D91" s="36">
+      <c r="D91" s="34">
         <v>811.39817000000005</v>
       </c>
-      <c r="E91" s="36">
+      <c r="E91" s="34">
         <v>745.77777000000003</v>
       </c>
-      <c r="F91" s="36">
+      <c r="F91" s="34">
         <v>1557.1759400000001</v>
       </c>
-      <c r="G91" s="34">
+      <c r="G91" s="32">
         <v>20.634704180389164</v>
       </c>
-      <c r="H91" s="34">
+      <c r="H91" s="32">
         <v>18.553292572954316</v>
       </c>
-      <c r="I91" s="34">
+      <c r="I91" s="32">
         <v>19.582553248431527</v>
       </c>
     </row>
     <row r="92" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="30" t="s">
+      <c r="B92" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C92" s="15">
+      <c r="C92" s="13">
         <v>2015</v>
       </c>
-      <c r="D92" s="35">
+      <c r="D92" s="33">
         <v>36.304690000000001</v>
       </c>
-      <c r="E92" s="35">
+      <c r="E92" s="33">
         <v>30.343330000000002</v>
       </c>
-      <c r="F92" s="35">
+      <c r="F92" s="33">
         <v>66.648020000000002</v>
       </c>
-      <c r="G92" s="17">
+      <c r="G92" s="15">
         <v>34.88208017153233</v>
       </c>
-      <c r="H92" s="17">
+      <c r="H92" s="15">
         <v>31.724918474652647</v>
       </c>
-      <c r="I92" s="17">
+      <c r="I92" s="15">
         <v>33.370154249295929</v>
       </c>
     </row>
     <row r="93" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="30" t="s">
+      <c r="B93" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C93" s="15">
+      <c r="C93" s="13">
         <v>2015</v>
       </c>
-      <c r="D93" s="35">
+      <c r="D93" s="33">
         <v>31.93609</v>
       </c>
-      <c r="E93" s="35">
+      <c r="E93" s="33">
         <v>32.330849999999998</v>
       </c>
-      <c r="F93" s="35">
+      <c r="F93" s="33">
         <v>64.266940000000005</v>
       </c>
-      <c r="G93" s="17">
+      <c r="G93" s="15">
         <v>31.8740344423442</v>
       </c>
-      <c r="H93" s="17">
+      <c r="H93" s="15">
         <v>32.274917567854907</v>
       </c>
-      <c r="I93" s="17">
+      <c r="I93" s="15">
         <v>32.0744546072454</v>
       </c>
     </row>
     <row r="94" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="30" t="s">
+      <c r="B94" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C94" s="15">
+      <c r="C94" s="13">
         <v>2015</v>
       </c>
-      <c r="D94" s="35">
+      <c r="D94" s="33">
         <v>98.078310000000002</v>
       </c>
-      <c r="E94" s="35">
+      <c r="E94" s="33">
         <v>84.3322</v>
       </c>
-      <c r="F94" s="35">
+      <c r="F94" s="33">
         <v>182.41050999999999</v>
       </c>
-      <c r="G94" s="17">
+      <c r="G94" s="15">
         <v>30.187073824918357</v>
       </c>
-      <c r="H94" s="17">
+      <c r="H94" s="15">
         <v>27.649395791381913</v>
       </c>
-      <c r="I94" s="17">
+      <c r="I94" s="15">
         <v>28.958312053745814</v>
       </c>
     </row>
     <row r="95" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="30" t="s">
+      <c r="B95" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C95" s="15">
+      <c r="C95" s="13">
         <v>2015</v>
       </c>
-      <c r="D95" s="35">
+      <c r="D95" s="33">
         <v>52.439019999999999</v>
       </c>
-      <c r="E95" s="35">
+      <c r="E95" s="33">
         <v>43.9328</v>
       </c>
-      <c r="F95" s="35">
+      <c r="F95" s="33">
         <v>96.37182</v>
       </c>
-      <c r="G95" s="17">
+      <c r="G95" s="15">
         <v>23.916923715309036</v>
       </c>
-      <c r="H95" s="17">
+      <c r="H95" s="15">
         <v>21.845651438521291</v>
       </c>
-      <c r="I95" s="17">
+      <c r="I95" s="15">
         <v>22.926002010560754</v>
       </c>
     </row>
     <row r="96" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="30" t="s">
+      <c r="B96" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C96" s="15">
+      <c r="C96" s="13">
         <v>2015</v>
       </c>
-      <c r="D96" s="35">
+      <c r="D96" s="33">
         <v>208.27923000000001</v>
       </c>
-      <c r="E96" s="35">
+      <c r="E96" s="33">
         <v>204.0214</v>
       </c>
-      <c r="F96" s="35">
+      <c r="F96" s="33">
         <v>412.30063000000001</v>
       </c>
-      <c r="G96" s="17">
+      <c r="G96" s="15">
         <v>22.963917023656307</v>
       </c>
-      <c r="H96" s="17">
+      <c r="H96" s="15">
         <v>23.109530323257431</v>
       </c>
-      <c r="I96" s="17">
+      <c r="I96" s="15">
         <v>23.035741728463314</v>
       </c>
     </row>
     <row r="97" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="30" t="s">
+      <c r="B97" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C97" s="15">
+      <c r="C97" s="13">
         <v>2015</v>
       </c>
-      <c r="D97" s="35">
+      <c r="D97" s="33">
         <v>218.73973000000001</v>
       </c>
-      <c r="E97" s="35">
+      <c r="E97" s="33">
         <v>220.87495000000001</v>
       </c>
-      <c r="F97" s="35">
+      <c r="F97" s="33">
         <v>439.61468000000002</v>
       </c>
-      <c r="G97" s="17">
+      <c r="G97" s="15">
         <v>15.168599952445682</v>
       </c>
-      <c r="H97" s="17">
+      <c r="H97" s="15">
         <v>15.239739492472367</v>
       </c>
-      <c r="I97" s="17">
+      <c r="I97" s="15">
         <v>15.204259272203815</v>
       </c>
     </row>
     <row r="98" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="30" t="s">
+      <c r="B98" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C98" s="15">
+      <c r="C98" s="13">
         <v>2015</v>
       </c>
-      <c r="D98" s="35">
+      <c r="D98" s="33">
         <v>56.28642</v>
       </c>
-      <c r="E98" s="35">
+      <c r="E98" s="33">
         <v>55.830289999999998</v>
       </c>
-      <c r="F98" s="35">
+      <c r="F98" s="33">
         <v>112.11671</v>
       </c>
-      <c r="G98" s="17">
+      <c r="G98" s="15">
         <v>9.473900647083827</v>
       </c>
-      <c r="H98" s="17">
+      <c r="H98" s="15">
         <v>8.4081577170026112</v>
       </c>
-      <c r="I98" s="17">
+      <c r="I98" s="15">
         <v>8.9114316007047716</v>
       </c>
     </row>
     <row r="99" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="30" t="s">
+      <c r="B99" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C99" s="15">
+      <c r="C99" s="13">
         <v>2015</v>
       </c>
-      <c r="D99" s="35">
+      <c r="D99" s="33">
         <v>10.06043</v>
       </c>
-      <c r="E99" s="35">
+      <c r="E99" s="33">
         <v>16.409959999999998</v>
       </c>
-      <c r="F99" s="35">
+      <c r="F99" s="33">
         <v>26.470389999999998</v>
       </c>
-      <c r="G99" s="37">
+      <c r="G99" s="35">
         <v>5.9469005854313783</v>
       </c>
-      <c r="H99" s="17">
+      <c r="H99" s="15">
         <v>5.6318809028287449</v>
       </c>
-      <c r="I99" s="17">
+      <c r="I99" s="15">
         <v>5.7475958434398793</v>
       </c>
     </row>
     <row r="100" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="32" t="s">
+      <c r="B100" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C100" s="18">
+      <c r="C100" s="16">
         <v>2015</v>
       </c>
-      <c r="D100" s="36">
+      <c r="D100" s="34">
         <v>712.12392</v>
       </c>
-      <c r="E100" s="36">
+      <c r="E100" s="34">
         <v>688.07578999999998</v>
       </c>
-      <c r="F100" s="36">
+      <c r="F100" s="34">
         <v>1400.1997099999999</v>
       </c>
-      <c r="G100" s="34">
+      <c r="G100" s="32">
         <v>18.445163297865253</v>
       </c>
-      <c r="H100" s="34">
+      <c r="H100" s="32">
         <v>17.247221093805312</v>
       </c>
-      <c r="I100" s="34">
+      <c r="I100" s="32">
         <v>17.836370489185171</v>
       </c>
     </row>
     <row r="101" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="30" t="s">
+      <c r="B101" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C101" s="15">
+      <c r="C101" s="13">
         <v>2014</v>
       </c>
-      <c r="D101" s="35">
+      <c r="D101" s="33">
         <v>32.210149999999999</v>
       </c>
-      <c r="E101" s="35">
+      <c r="E101" s="33">
         <v>31.520400000000002</v>
       </c>
-      <c r="F101" s="35">
+      <c r="F101" s="33">
         <v>63.730550000000001</v>
       </c>
-      <c r="G101" s="17">
+      <c r="G101" s="15">
         <v>31.584362704856144</v>
       </c>
-      <c r="H101" s="17">
+      <c r="H101" s="15">
         <v>33.210208469380724</v>
       </c>
-      <c r="I101" s="17">
+      <c r="I101" s="15">
         <v>32.368097206047338</v>
       </c>
     </row>
     <row r="102" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="30" t="s">
+      <c r="B102" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C102" s="15">
+      <c r="C102" s="13">
         <v>2014</v>
       </c>
-      <c r="D102" s="35">
+      <c r="D102" s="33">
         <v>30.18083</v>
       </c>
-      <c r="E102" s="35">
+      <c r="E102" s="33">
         <v>29.92632</v>
       </c>
-      <c r="F102" s="35">
+      <c r="F102" s="33">
         <v>60.107150000000004</v>
       </c>
-      <c r="G102" s="17">
+      <c r="G102" s="15">
         <v>31.103820315966136</v>
       </c>
-      <c r="H102" s="17">
+      <c r="H102" s="15">
         <v>30.996354450906065</v>
       </c>
-      <c r="I102" s="17">
+      <c r="I102" s="15">
         <v>31.050221918105152</v>
       </c>
     </row>
     <row r="103" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="30" t="s">
+      <c r="B103" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C103" s="15">
+      <c r="C103" s="13">
         <v>2014</v>
       </c>
-      <c r="D103" s="35">
+      <c r="D103" s="33">
         <v>97.20684</v>
       </c>
-      <c r="E103" s="35">
+      <c r="E103" s="33">
         <v>86.030470000000008</v>
       </c>
-      <c r="F103" s="35">
+      <c r="F103" s="33">
         <v>183.23731000000001</v>
       </c>
-      <c r="G103" s="17">
+      <c r="G103" s="15">
         <v>28.97923447079458</v>
       </c>
-      <c r="H103" s="17">
+      <c r="H103" s="15">
         <v>27.265055137354217</v>
       </c>
-      <c r="I103" s="17">
+      <c r="I103" s="15">
         <v>28.148348953894203</v>
       </c>
     </row>
     <row r="104" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="30" t="s">
+      <c r="B104" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C104" s="15">
+      <c r="C104" s="13">
         <v>2014</v>
       </c>
-      <c r="D104" s="35">
+      <c r="D104" s="33">
         <v>49.866639999999997</v>
       </c>
-      <c r="E104" s="35">
+      <c r="E104" s="33">
         <v>44.529650000000004</v>
       </c>
-      <c r="F104" s="35">
+      <c r="F104" s="33">
         <v>94.396289999999993</v>
       </c>
-      <c r="G104" s="17">
+      <c r="G104" s="15">
         <v>23.506337239629858</v>
       </c>
-      <c r="H104" s="17">
+      <c r="H104" s="15">
         <v>21.469018920800394</v>
       </c>
-      <c r="I104" s="17">
+      <c r="I104" s="15">
         <v>22.499156784743178</v>
       </c>
     </row>
     <row r="105" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="30" t="s">
+      <c r="B105" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C105" s="15">
+      <c r="C105" s="13">
         <v>2014</v>
       </c>
-      <c r="D105" s="35">
+      <c r="D105" s="33">
         <v>198.49485000000001</v>
       </c>
-      <c r="E105" s="35">
+      <c r="E105" s="33">
         <v>196.50056000000001</v>
       </c>
-      <c r="F105" s="35">
+      <c r="F105" s="33">
         <v>394.99540999999999</v>
       </c>
-      <c r="G105" s="17">
+      <c r="G105" s="15">
         <v>22.120843721344894</v>
       </c>
-      <c r="H105" s="17">
+      <c r="H105" s="15">
         <v>22.548961804003607</v>
       </c>
-      <c r="I105" s="17">
+      <c r="I105" s="15">
         <v>22.331770598172699</v>
       </c>
     </row>
     <row r="106" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="30" t="s">
+      <c r="B106" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C106" s="15">
+      <c r="C106" s="13">
         <v>2014</v>
       </c>
-      <c r="D106" s="35">
+      <c r="D106" s="33">
         <v>209.40410999999997</v>
       </c>
-      <c r="E106" s="35">
+      <c r="E106" s="33">
         <v>215.30840000000001</v>
       </c>
-      <c r="F106" s="35">
+      <c r="F106" s="33">
         <v>424.71250999999995</v>
       </c>
-      <c r="G106" s="17">
+      <c r="G106" s="15">
         <v>14.671498974024136</v>
       </c>
-      <c r="H106" s="17">
+      <c r="H106" s="15">
         <v>15.103697993720012</v>
       </c>
-      <c r="I106" s="17">
+      <c r="I106" s="15">
         <v>14.887465868545332</v>
       </c>
     </row>
     <row r="107" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="30" t="s">
+      <c r="B107" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C107" s="15">
+      <c r="C107" s="13">
         <v>2014</v>
       </c>
-      <c r="D107" s="35">
+      <c r="D107" s="33">
         <v>56.056249999999999</v>
       </c>
-      <c r="E107" s="35">
+      <c r="E107" s="33">
         <v>52.526769999999999</v>
       </c>
-      <c r="F107" s="35">
+      <c r="F107" s="33">
         <v>108.58302</v>
       </c>
-      <c r="G107" s="17">
+      <c r="G107" s="15">
         <v>9.3756841771985702</v>
       </c>
-      <c r="H107" s="17">
+      <c r="H107" s="15">
         <v>7.8285535830302164</v>
       </c>
-      <c r="I107" s="17">
+      <c r="I107" s="15">
         <v>8.557568681563124</v>
       </c>
     </row>
     <row r="108" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="30" t="s">
+      <c r="B108" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C108" s="15">
+      <c r="C108" s="13">
         <v>2014</v>
       </c>
-      <c r="D108" s="35">
+      <c r="D108" s="33">
         <v>9.3628600000000013</v>
       </c>
-      <c r="E108" s="35">
+      <c r="E108" s="33">
         <v>18.189400000000003</v>
       </c>
-      <c r="F108" s="35">
+      <c r="F108" s="33">
         <v>27.552260000000004</v>
       </c>
-      <c r="G108" s="37">
+      <c r="G108" s="35">
         <v>5.8678779548369073</v>
       </c>
-      <c r="H108" s="17">
+      <c r="H108" s="15">
         <v>6.3133258052220267</v>
       </c>
-      <c r="I108" s="17">
+      <c r="I108" s="15">
         <v>6.1545574568264731</v>
       </c>
     </row>
     <row r="109" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="32" t="s">
+      <c r="B109" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C109" s="18">
+      <c r="C109" s="16">
         <v>2014</v>
       </c>
-      <c r="D109" s="36">
+      <c r="D109" s="34">
         <v>682.78253000000007</v>
       </c>
-      <c r="E109" s="36">
+      <c r="E109" s="34">
         <v>674.53195999999991</v>
       </c>
-      <c r="F109" s="36">
+      <c r="F109" s="34">
         <v>1357.31449</v>
       </c>
-      <c r="G109" s="34">
+      <c r="G109" s="32">
         <v>17.83351649983074</v>
       </c>
-      <c r="H109" s="34">
+      <c r="H109" s="32">
         <v>16.98877828631047</v>
       </c>
-      <c r="I109" s="34">
+      <c r="I109" s="32">
         <v>17.40346761281436</v>
       </c>
     </row>
     <row r="110" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="30" t="s">
+      <c r="B110" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C110" s="15">
+      <c r="C110" s="13">
         <v>2013</v>
       </c>
-      <c r="D110" s="35">
+      <c r="D110" s="33">
         <v>32.36027</v>
       </c>
-      <c r="E110" s="35">
+      <c r="E110" s="33">
         <v>25.282640000000001</v>
       </c>
-      <c r="F110" s="35">
+      <c r="F110" s="33">
         <v>57.642910000000001</v>
       </c>
-      <c r="G110" s="17">
+      <c r="G110" s="15">
         <v>33.743799524295646</v>
       </c>
-      <c r="H110" s="17">
+      <c r="H110" s="15">
         <v>28.357739042947728</v>
       </c>
-      <c r="I110" s="17">
+      <c r="I110" s="15">
         <v>31.148909289325744</v>
       </c>
     </row>
     <row r="111" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="30" t="s">
+      <c r="B111" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C111" s="15">
+      <c r="C111" s="13">
         <v>2013</v>
       </c>
-      <c r="D111" s="35">
+      <c r="D111" s="33">
         <v>32.661290000000001</v>
       </c>
-      <c r="E111" s="35">
+      <c r="E111" s="33">
         <v>29.116240000000001</v>
       </c>
-      <c r="F111" s="35">
+      <c r="F111" s="33">
         <v>61.777529999999999</v>
       </c>
-      <c r="G111" s="17">
+      <c r="G111" s="15">
         <v>31.93293800366207</v>
       </c>
-      <c r="H111" s="17">
+      <c r="H111" s="15">
         <v>29.783628570648229</v>
       </c>
-      <c r="I111" s="17">
+      <c r="I111" s="15">
         <v>30.882574587923845</v>
       </c>
     </row>
     <row r="112" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="30" t="s">
+      <c r="B112" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C112" s="15">
+      <c r="C112" s="13">
         <v>2013</v>
       </c>
-      <c r="D112" s="35">
+      <c r="D112" s="33">
         <v>91.491889999999998</v>
       </c>
-      <c r="E112" s="35">
+      <c r="E112" s="33">
         <v>90.232129999999998</v>
       </c>
-      <c r="F112" s="35">
+      <c r="F112" s="33">
         <v>181.72402</v>
       </c>
-      <c r="G112" s="17">
+      <c r="G112" s="15">
         <v>26.680289109327465</v>
       </c>
-      <c r="H112" s="17">
+      <c r="H112" s="15">
         <v>27.583086852697352</v>
       </c>
-      <c r="I112" s="17">
+      <c r="I112" s="15">
         <v>27.121049916611938</v>
       </c>
     </row>
     <row r="113" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="30" t="s">
+      <c r="B113" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C113" s="15">
+      <c r="C113" s="13">
         <v>2013</v>
       </c>
-      <c r="D113" s="35">
+      <c r="D113" s="33">
         <v>48.30245</v>
       </c>
-      <c r="E113" s="35">
+      <c r="E113" s="33">
         <v>45.75808</v>
       </c>
-      <c r="F113" s="35">
+      <c r="F113" s="33">
         <v>94.06053</v>
       </c>
-      <c r="G113" s="17">
+      <c r="G113" s="15">
         <v>22.725873016238953</v>
       </c>
-      <c r="H113" s="17">
+      <c r="H113" s="15">
         <v>21.96633862992655</v>
       </c>
-      <c r="I113" s="17">
+      <c r="I113" s="15">
         <v>22.349926353296929</v>
       </c>
     </row>
     <row r="114" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="30" t="s">
+      <c r="B114" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C114" s="15">
+      <c r="C114" s="13">
         <v>2013</v>
       </c>
-      <c r="D114" s="35">
+      <c r="D114" s="33">
         <v>201.90835000000001</v>
       </c>
-      <c r="E114" s="35">
+      <c r="E114" s="33">
         <v>203.49382</v>
       </c>
-      <c r="F114" s="35">
+      <c r="F114" s="33">
         <v>405.40217000000001</v>
       </c>
-      <c r="G114" s="17">
+      <c r="G114" s="15">
         <v>22.790098620722162</v>
       </c>
-      <c r="H114" s="17">
+      <c r="H114" s="15">
         <v>23.473077788381808</v>
       </c>
-      <c r="I114" s="17">
+      <c r="I114" s="15">
         <v>23.127882127160458</v>
       </c>
     </row>
     <row r="115" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="30" t="s">
+      <c r="B115" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C115" s="15">
+      <c r="C115" s="13">
         <v>2013</v>
       </c>
-      <c r="D115" s="35">
+      <c r="D115" s="33">
         <v>210.08564000000001</v>
       </c>
-      <c r="E115" s="35">
+      <c r="E115" s="33">
         <v>206.28954999999999</v>
       </c>
-      <c r="F115" s="35">
+      <c r="F115" s="33">
         <v>416.37518999999998</v>
       </c>
-      <c r="G115" s="17">
+      <c r="G115" s="15">
         <v>14.643827899240986</v>
       </c>
-      <c r="H115" s="17">
+      <c r="H115" s="15">
         <v>14.359308350235494</v>
       </c>
-      <c r="I115" s="17">
+      <c r="I115" s="15">
         <v>14.501469534978423</v>
       </c>
     </row>
     <row r="116" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="30" t="s">
+      <c r="B116" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C116" s="15">
+      <c r="C116" s="13">
         <v>2013</v>
       </c>
-      <c r="D116" s="35">
+      <c r="D116" s="33">
         <v>53.528129999999997</v>
       </c>
-      <c r="E116" s="35">
+      <c r="E116" s="33">
         <v>48.622390000000003</v>
       </c>
-      <c r="F116" s="35">
+      <c r="F116" s="33">
         <v>102.15052</v>
       </c>
-      <c r="G116" s="17">
+      <c r="G116" s="15">
         <v>9.0738655068167393</v>
       </c>
-      <c r="H116" s="17">
+      <c r="H116" s="15">
         <v>7.3257203825905197</v>
       </c>
-      <c r="I116" s="17">
+      <c r="I116" s="15">
         <v>8.1483330796979807</v>
       </c>
     </row>
     <row r="117" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="30" t="s">
+      <c r="B117" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C117" s="15">
+      <c r="C117" s="13">
         <v>2013</v>
       </c>
-      <c r="D117" s="35">
+      <c r="D117" s="33">
         <v>8.5968799999999987</v>
       </c>
-      <c r="E117" s="35">
+      <c r="E117" s="33">
         <v>18.341570000000001</v>
       </c>
-      <c r="F117" s="35">
+      <c r="F117" s="33">
         <v>26.93845</v>
       </c>
-      <c r="G117" s="37">
+      <c r="G117" s="35">
         <v>5.7894422454163808</v>
       </c>
-      <c r="H117" s="17">
+      <c r="H117" s="15">
         <v>6.5071108757935052</v>
       </c>
-      <c r="I117" s="17">
+      <c r="I117" s="15">
         <v>6.2594860545427791</v>
       </c>
     </row>
     <row r="118" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="32" t="s">
+      <c r="B118" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C118" s="18">
+      <c r="C118" s="16">
         <v>2013</v>
       </c>
-      <c r="D118" s="36">
+      <c r="D118" s="34">
         <v>678.93489</v>
       </c>
-      <c r="E118" s="36">
+      <c r="E118" s="34">
         <v>667.13641000000007</v>
       </c>
-      <c r="F118" s="36">
+      <c r="F118" s="34">
         <v>1346.0713000000001</v>
       </c>
-      <c r="G118" s="34">
+      <c r="G118" s="32">
         <v>17.807494852622437</v>
       </c>
-      <c r="H118" s="34">
+      <c r="H118" s="32">
         <v>16.798116779819892</v>
       </c>
-      <c r="I118" s="34">
+      <c r="I118" s="32">
         <v>17.292506051215074</v>
       </c>
     </row>
     <row r="119" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="30" t="s">
+      <c r="B119" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C119" s="15">
+      <c r="C119" s="13">
         <v>2012</v>
       </c>
-      <c r="D119" s="35">
+      <c r="D119" s="33">
         <v>27.899039999999999</v>
       </c>
-      <c r="E119" s="35">
+      <c r="E119" s="33">
         <v>26.68881</v>
       </c>
-      <c r="F119" s="35">
+      <c r="F119" s="33">
         <v>54.587850000000003</v>
       </c>
-      <c r="G119" s="17">
+      <c r="G119" s="15">
         <v>30.592173002827078</v>
       </c>
-      <c r="H119" s="17">
+      <c r="H119" s="15">
         <v>29.375334119425467</v>
       </c>
-      <c r="I119" s="17">
+      <c r="I119" s="15">
         <v>29.984897101721135</v>
       </c>
     </row>
     <row r="120" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="30" t="s">
+      <c r="B120" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C120" s="15">
+      <c r="C120" s="13">
         <v>2012</v>
       </c>
-      <c r="D120" s="35">
+      <c r="D120" s="33">
         <v>30.914630000000002</v>
       </c>
-      <c r="E120" s="35">
+      <c r="E120" s="33">
         <v>29.043800000000001</v>
       </c>
-      <c r="F120" s="35">
+      <c r="F120" s="33">
         <v>59.958430000000007</v>
       </c>
-      <c r="G120" s="17">
+      <c r="G120" s="15">
         <v>29.840258354189913</v>
       </c>
-      <c r="H120" s="17">
+      <c r="H120" s="15">
         <v>29.719025167513458</v>
       </c>
-      <c r="I120" s="17">
+      <c r="I120" s="15">
         <v>29.781409853891439</v>
       </c>
     </row>
     <row r="121" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="30" t="s">
+      <c r="B121" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C121" s="15">
+      <c r="C121" s="13">
         <v>2012</v>
       </c>
-      <c r="D121" s="35">
+      <c r="D121" s="33">
         <v>93.994509999999991</v>
       </c>
-      <c r="E121" s="35">
+      <c r="E121" s="33">
         <v>89.781070000000014</v>
       </c>
-      <c r="F121" s="35">
+      <c r="F121" s="33">
         <v>183.77557999999999</v>
       </c>
-      <c r="G121" s="17">
+      <c r="G121" s="15">
         <v>26.311067495636863</v>
       </c>
-      <c r="H121" s="17">
+      <c r="H121" s="15">
         <v>26.768388311483132</v>
       </c>
-      <c r="I121" s="17">
+      <c r="I121" s="15">
         <v>26.532516722001827</v>
       </c>
     </row>
     <row r="122" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="30" t="s">
+      <c r="B122" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C122" s="15">
+      <c r="C122" s="13">
         <v>2012</v>
       </c>
-      <c r="D122" s="35">
+      <c r="D122" s="33">
         <v>49.122140000000002</v>
       </c>
-      <c r="E122" s="35">
+      <c r="E122" s="33">
         <v>44.97681</v>
       </c>
-      <c r="F122" s="35">
+      <c r="F122" s="33">
         <v>94.098950000000002</v>
       </c>
-      <c r="G122" s="17">
+      <c r="G122" s="15">
         <v>22.160941427240502</v>
       </c>
-      <c r="H122" s="17">
+      <c r="H122" s="15">
         <v>21.130937713106736</v>
       </c>
-      <c r="I122" s="17">
+      <c r="I122" s="15">
         <v>21.656384870611664</v>
       </c>
     </row>
     <row r="123" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="30" t="s">
+      <c r="B123" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C123" s="15">
+      <c r="C123" s="13">
         <v>2012</v>
       </c>
-      <c r="D123" s="35">
+      <c r="D123" s="33">
         <v>190.89631</v>
       </c>
-      <c r="E123" s="35">
+      <c r="E123" s="33">
         <v>193.85954000000001</v>
       </c>
-      <c r="F123" s="35">
+      <c r="F123" s="33">
         <v>384.75585000000001</v>
       </c>
-      <c r="G123" s="17">
+      <c r="G123" s="15">
         <v>21.772778202146693</v>
       </c>
-      <c r="H123" s="17">
+      <c r="H123" s="15">
         <v>22.513417557204555</v>
       </c>
-      <c r="I123" s="17">
+      <c r="I123" s="15">
         <v>22.139756296518566</v>
       </c>
     </row>
     <row r="124" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="30" t="s">
+      <c r="B124" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C124" s="15">
+      <c r="C124" s="13">
         <v>2012</v>
       </c>
-      <c r="D124" s="35">
+      <c r="D124" s="33">
         <v>198.17562000000001</v>
       </c>
-      <c r="E124" s="35">
+      <c r="E124" s="33">
         <v>199.38325</v>
       </c>
-      <c r="F124" s="35">
+      <c r="F124" s="33">
         <v>397.55887000000001</v>
       </c>
-      <c r="G124" s="17">
+      <c r="G124" s="15">
         <v>13.739469891416062</v>
       </c>
-      <c r="H124" s="17">
+      <c r="H124" s="15">
         <v>13.937066621035365</v>
       </c>
-      <c r="I124" s="17">
+      <c r="I124" s="15">
         <v>13.837862987363501</v>
       </c>
     </row>
     <row r="125" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="30" t="s">
+      <c r="B125" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C125" s="15">
+      <c r="C125" s="13">
         <v>2012</v>
       </c>
-      <c r="D125" s="35">
+      <c r="D125" s="33">
         <v>50.494540000000001</v>
       </c>
-      <c r="E125" s="35">
+      <c r="E125" s="33">
         <v>49.992899999999999</v>
       </c>
-      <c r="F125" s="35">
+      <c r="F125" s="33">
         <v>100.48743999999999</v>
       </c>
-      <c r="G125" s="17">
+      <c r="G125" s="15">
         <v>8.8138419161653658</v>
       </c>
-      <c r="H125" s="17">
+      <c r="H125" s="15">
         <v>7.5933494926557641</v>
       </c>
-      <c r="I125" s="17">
+      <c r="I125" s="15">
         <v>8.1612315803055644</v>
       </c>
     </row>
     <row r="126" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="30" t="s">
+      <c r="B126" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C126" s="15">
+      <c r="C126" s="13">
         <v>2012</v>
       </c>
-      <c r="D126" s="35">
+      <c r="D126" s="33">
         <v>8.1997999999999998</v>
       </c>
-      <c r="E126" s="35">
+      <c r="E126" s="33">
         <v>15.310549999999999</v>
       </c>
-      <c r="F126" s="35">
+      <c r="F126" s="33">
         <v>23.510349999999999</v>
       </c>
-      <c r="G126" s="37">
+      <c r="G126" s="35">
         <v>5.7415561705238956</v>
       </c>
-      <c r="H126" s="17">
+      <c r="H126" s="15">
         <v>5.4127778969182492</v>
       </c>
-      <c r="I126" s="17">
+      <c r="I126" s="15">
         <v>5.5230839389136737</v>
       </c>
     </row>
     <row r="127" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="32" t="s">
+      <c r="B127" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C127" s="18">
+      <c r="C127" s="16">
         <v>2012</v>
       </c>
-      <c r="D127" s="36">
+      <c r="D127" s="34">
         <v>649.69659000000001</v>
       </c>
-      <c r="E127" s="36">
+      <c r="E127" s="34">
         <v>649.03673000000003</v>
       </c>
-      <c r="F127" s="36">
+      <c r="F127" s="34">
         <v>1298.73332</v>
       </c>
-      <c r="G127" s="34">
+      <c r="G127" s="32">
         <v>17.058831624170956</v>
       </c>
-      <c r="H127" s="34">
+      <c r="H127" s="32">
         <v>16.34956823611725</v>
       </c>
-      <c r="I127" s="34">
+      <c r="I127" s="32">
         <v>16.696851168695275</v>
       </c>
     </row>
     <row r="128" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B128" s="30" t="s">
+      <c r="B128" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C128" s="15">
+      <c r="C128" s="13">
         <v>2011</v>
       </c>
-      <c r="D128" s="35">
+      <c r="D128" s="33">
         <v>29.840169999999997</v>
       </c>
-      <c r="E128" s="35">
+      <c r="E128" s="33">
         <v>25.880860000000002</v>
       </c>
-      <c r="F128" s="35">
+      <c r="F128" s="33">
         <v>55.721029999999999</v>
       </c>
-      <c r="G128" s="17">
+      <c r="G128" s="15">
         <v>31.593217618539267</v>
       </c>
-      <c r="H128" s="17">
+      <c r="H128" s="15">
         <v>28.287714533543657</v>
       </c>
-      <c r="I128" s="17">
+      <c r="I128" s="15">
         <v>29.96677309909057</v>
       </c>
     </row>
     <row r="129" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="30" t="s">
+      <c r="B129" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C129" s="15">
+      <c r="C129" s="13">
         <v>2011</v>
       </c>
-      <c r="D129" s="35">
+      <c r="D129" s="33">
         <v>26.734290000000001</v>
       </c>
-      <c r="E129" s="35">
+      <c r="E129" s="33">
         <v>29.922000000000001</v>
       </c>
-      <c r="F129" s="35">
+      <c r="F129" s="33">
         <v>56.656289999999998</v>
       </c>
-      <c r="G129" s="17">
+      <c r="G129" s="15">
         <v>27.019456041002343</v>
       </c>
-      <c r="H129" s="17">
+      <c r="H129" s="15">
         <v>30.581067884513079</v>
       </c>
-      <c r="I129" s="17">
+      <c r="I129" s="15">
         <v>28.790310089809694</v>
       </c>
     </row>
     <row r="130" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="30" t="s">
+      <c r="B130" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C130" s="15">
+      <c r="C130" s="13">
         <v>2011</v>
       </c>
-      <c r="D130" s="35">
+      <c r="D130" s="33">
         <v>94.719399999999993</v>
       </c>
-      <c r="E130" s="35">
+      <c r="E130" s="33">
         <v>86.884129999999999</v>
       </c>
-      <c r="F130" s="35">
+      <c r="F130" s="33">
         <v>181.60352999999998</v>
       </c>
-      <c r="G130" s="17">
+      <c r="G130" s="15">
         <v>25.710748447559862</v>
       </c>
-      <c r="H130" s="17">
+      <c r="H130" s="15">
         <v>25.232308144324843</v>
       </c>
-      <c r="I130" s="17">
+      <c r="I130" s="15">
         <v>25.479606027285691</v>
       </c>
     </row>
     <row r="131" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="30" t="s">
+      <c r="B131" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C131" s="15">
+      <c r="C131" s="13">
         <v>2011</v>
       </c>
-      <c r="D131" s="35">
+      <c r="D131" s="33">
         <v>48.484199999999994</v>
       </c>
-      <c r="E131" s="35">
+      <c r="E131" s="33">
         <v>45.07573</v>
       </c>
-      <c r="F131" s="35">
+      <c r="F131" s="33">
         <v>93.559929999999994</v>
       </c>
-      <c r="G131" s="17">
+      <c r="G131" s="15">
         <v>21.791702584129112</v>
       </c>
-      <c r="H131" s="17">
+      <c r="H131" s="15">
         <v>21.243409524499839</v>
       </c>
-      <c r="I131" s="17">
+      <c r="I131" s="15">
         <v>21.524053677109872</v>
       </c>
     </row>
     <row r="132" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="30" t="s">
+      <c r="B132" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C132" s="15">
+      <c r="C132" s="13">
         <v>2011</v>
       </c>
-      <c r="D132" s="35">
+      <c r="D132" s="33">
         <v>188.87361999999999</v>
       </c>
-      <c r="E132" s="35">
+      <c r="E132" s="33">
         <v>190.72764000000001</v>
       </c>
-      <c r="F132" s="35">
+      <c r="F132" s="33">
         <v>379.60126000000002</v>
       </c>
-      <c r="G132" s="17">
+      <c r="G132" s="15">
         <v>21.479743427579802</v>
       </c>
-      <c r="H132" s="17">
+      <c r="H132" s="15">
         <v>22.091781582977454</v>
       </c>
-      <c r="I132" s="17">
+      <c r="I132" s="15">
         <v>21.782958375991964</v>
       </c>
     </row>
     <row r="133" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="30" t="s">
+      <c r="B133" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C133" s="15">
+      <c r="C133" s="13">
         <v>2011</v>
       </c>
-      <c r="D133" s="35">
+      <c r="D133" s="33">
         <v>188.17420000000001</v>
       </c>
-      <c r="E133" s="35">
+      <c r="E133" s="33">
         <v>198.01193000000001</v>
       </c>
-      <c r="F133" s="35">
+      <c r="F133" s="33">
         <v>386.18613000000005</v>
       </c>
-      <c r="G133" s="17">
+      <c r="G133" s="15">
         <v>13.179953025165963</v>
       </c>
-      <c r="H133" s="17">
+      <c r="H133" s="15">
         <v>13.855236919233258</v>
       </c>
-      <c r="I133" s="17">
+      <c r="I133" s="15">
         <v>13.51776258418947</v>
       </c>
     </row>
     <row r="134" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B134" s="30" t="s">
+      <c r="B134" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C134" s="15">
+      <c r="C134" s="13">
         <v>2011</v>
       </c>
-      <c r="D134" s="35">
+      <c r="D134" s="33">
         <v>47.865230000000004</v>
       </c>
-      <c r="E134" s="35">
+      <c r="E134" s="33">
         <v>44.14781</v>
       </c>
-      <c r="F134" s="35">
+      <c r="F134" s="33">
         <v>92.013040000000004</v>
       </c>
-      <c r="G134" s="17">
+      <c r="G134" s="15">
         <v>8.3832769202428352</v>
       </c>
-      <c r="H134" s="17">
+      <c r="H134" s="15">
         <v>6.7513228202605635</v>
       </c>
-      <c r="I134" s="17">
+      <c r="I134" s="15">
         <v>7.512039153338784</v>
       </c>
     </row>
     <row r="135" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B135" s="30" t="s">
+      <c r="B135" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C135" s="15">
+      <c r="C135" s="13">
         <v>2011</v>
       </c>
-      <c r="D135" s="35">
+      <c r="D135" s="33">
         <v>7.9523599999999997</v>
       </c>
-      <c r="E135" s="35">
+      <c r="E135" s="33">
         <v>14.308399999999999</v>
       </c>
-      <c r="F135" s="35">
+      <c r="F135" s="33">
         <v>22.260759999999998</v>
       </c>
-      <c r="G135" s="37">
+      <c r="G135" s="35">
         <v>5.6099959507144099</v>
       </c>
-      <c r="H135" s="17">
+      <c r="H135" s="15">
         <v>5.0740766825175712</v>
       </c>
-      <c r="I135" s="17">
+      <c r="I135" s="15">
         <v>5.2533557909379258</v>
       </c>
     </row>
     <row r="136" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B136" s="32" t="s">
+      <c r="B136" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C136" s="18">
+      <c r="C136" s="16">
         <v>2011</v>
       </c>
-      <c r="D136" s="36">
+      <c r="D136" s="34">
         <v>632.64346999999998</v>
       </c>
-      <c r="E136" s="36">
+      <c r="E136" s="34">
         <v>634.95849999999996</v>
       </c>
-      <c r="F136" s="36">
+      <c r="F136" s="34">
         <v>1267.6019699999999</v>
       </c>
-      <c r="G136" s="34">
+      <c r="G136" s="32">
         <v>16.630813462846206</v>
       </c>
-      <c r="H136" s="34">
+      <c r="H136" s="32">
         <v>15.97679518505117</v>
       </c>
-      <c r="I136" s="34">
+      <c r="I136" s="32">
         <v>16.296648469859321</v>
       </c>
     </row>
     <row r="137" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B137" s="30" t="s">
+      <c r="B137" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C137" s="15">
+      <c r="C137" s="13">
         <v>2010</v>
       </c>
-      <c r="D137" s="35">
+      <c r="D137" s="33">
         <v>29.643799999999999</v>
       </c>
-      <c r="E137" s="35">
+      <c r="E137" s="33">
         <v>30.121729999999999</v>
       </c>
-      <c r="F137" s="35">
+      <c r="F137" s="33">
         <v>59.765529999999998</v>
       </c>
-      <c r="G137" s="17">
+      <c r="G137" s="15">
         <v>32.246449646726902</v>
       </c>
-      <c r="H137" s="17">
+      <c r="H137" s="15">
         <v>31.49754266354358</v>
       </c>
-      <c r="I137" s="17">
+      <c r="I137" s="15">
         <v>31.864603109134482</v>
       </c>
     </row>
     <row r="138" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B138" s="30" t="s">
+      <c r="B138" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C138" s="15">
+      <c r="C138" s="13">
         <v>2010</v>
       </c>
-      <c r="D138" s="35">
+      <c r="D138" s="33">
         <v>34.164180000000002</v>
       </c>
-      <c r="E138" s="35">
+      <c r="E138" s="33">
         <v>27.649729999999998</v>
       </c>
-      <c r="F138" s="35">
+      <c r="F138" s="33">
         <v>61.813910000000007</v>
       </c>
-      <c r="G138" s="17">
+      <c r="G138" s="15">
         <v>32.760739408409215</v>
       </c>
-      <c r="H138" s="17">
+      <c r="H138" s="15">
         <v>28.646499265181628</v>
       </c>
-      <c r="I138" s="17">
+      <c r="I138" s="15">
         <v>30.783151322013126</v>
       </c>
     </row>
     <row r="139" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B139" s="30" t="s">
+      <c r="B139" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C139" s="15">
+      <c r="C139" s="13">
         <v>2010</v>
       </c>
-      <c r="D139" s="35">
+      <c r="D139" s="33">
         <v>91.291250000000005</v>
       </c>
-      <c r="E139" s="35">
+      <c r="E139" s="33">
         <v>87.064700000000002</v>
       </c>
-      <c r="F139" s="35">
+      <c r="F139" s="33">
         <v>178.35595000000001</v>
       </c>
-      <c r="G139" s="17">
+      <c r="G139" s="15">
         <v>24.775756555321941</v>
       </c>
-      <c r="H139" s="17">
+      <c r="H139" s="15">
         <v>25.284844270495238</v>
       </c>
-      <c r="I139" s="17">
+      <c r="I139" s="15">
         <v>25.021681928424805</v>
       </c>
     </row>
     <row r="140" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B140" s="30" t="s">
+      <c r="B140" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C140" s="15">
+      <c r="C140" s="13">
         <v>2010</v>
       </c>
-      <c r="D140" s="35">
+      <c r="D140" s="33">
         <v>52.348699999999994</v>
       </c>
-      <c r="E140" s="35">
+      <c r="E140" s="33">
         <v>46.44717</v>
       </c>
-      <c r="F140" s="35">
+      <c r="F140" s="33">
         <v>98.795869999999994</v>
       </c>
-      <c r="G140" s="17">
+      <c r="G140" s="15">
         <v>22.160273512401254</v>
       </c>
-      <c r="H140" s="17">
+      <c r="H140" s="15">
         <v>21.18062767883433</v>
       </c>
-      <c r="I140" s="17">
+      <c r="I140" s="15">
         <v>21.688662956359906</v>
       </c>
     </row>
     <row r="141" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="30" t="s">
+      <c r="B141" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C141" s="15">
+      <c r="C141" s="13">
         <v>2010</v>
       </c>
-      <c r="D141" s="35">
+      <c r="D141" s="33">
         <v>200.93583999999998</v>
       </c>
-      <c r="E141" s="35">
+      <c r="E141" s="33">
         <v>200.92060999999998</v>
       </c>
-      <c r="F141" s="35">
+      <c r="F141" s="33">
         <v>401.85645</v>
       </c>
-      <c r="G141" s="17">
+      <c r="G141" s="15">
         <v>21.931345913219076</v>
       </c>
-      <c r="H141" s="17">
+      <c r="H141" s="15">
         <v>22.598642036291178</v>
       </c>
-      <c r="I141" s="17">
+      <c r="I141" s="15">
         <v>22.259981509638905</v>
       </c>
     </row>
     <row r="142" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="30" t="s">
+      <c r="B142" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C142" s="15">
+      <c r="C142" s="13">
         <v>2010</v>
       </c>
-      <c r="D142" s="35">
+      <c r="D142" s="33">
         <v>209.07029</v>
       </c>
-      <c r="E142" s="35">
+      <c r="E142" s="33">
         <v>205.49851000000001</v>
       </c>
-      <c r="F142" s="35">
+      <c r="F142" s="33">
         <v>414.56880000000001</v>
       </c>
-      <c r="G142" s="17">
+      <c r="G142" s="15">
         <v>14.414754770005484</v>
       </c>
-      <c r="H142" s="17">
+      <c r="H142" s="15">
         <v>14.217330948309769</v>
       </c>
-      <c r="I142" s="17">
+      <c r="I142" s="15">
         <v>14.316212698698031</v>
       </c>
     </row>
     <row r="143" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="30" t="s">
+      <c r="B143" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C143" s="15">
+      <c r="C143" s="13">
         <v>2010</v>
       </c>
-      <c r="D143" s="35">
+      <c r="D143" s="33">
         <v>49.345260000000003</v>
       </c>
-      <c r="E143" s="35">
+      <c r="E143" s="33">
         <v>49.840389999999999</v>
       </c>
-      <c r="F143" s="35">
+      <c r="F143" s="33">
         <v>99.185649999999995</v>
       </c>
-      <c r="G143" s="17">
+      <c r="G143" s="15">
         <v>8.4230304393179978</v>
       </c>
-      <c r="H143" s="17">
+      <c r="H143" s="15">
         <v>7.4576737680502641</v>
       </c>
-      <c r="I143" s="17">
+      <c r="I143" s="15">
         <v>7.90861116488602</v>
       </c>
     </row>
     <row r="144" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="30" t="s">
+      <c r="B144" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C144" s="15">
+      <c r="C144" s="13">
         <v>2010</v>
       </c>
-      <c r="D144" s="35">
+      <c r="D144" s="33">
         <v>8.4805400000000013</v>
       </c>
-      <c r="E144" s="35">
+      <c r="E144" s="33">
         <v>12.00553</v>
       </c>
-      <c r="F144" s="35">
+      <c r="F144" s="33">
         <v>20.486069999999998</v>
       </c>
-      <c r="G144" s="37">
+      <c r="G144" s="35">
         <v>6.153879868530149</v>
       </c>
-      <c r="H144" s="17">
+      <c r="H144" s="15">
         <v>4.397047790191885</v>
       </c>
-      <c r="I144" s="17">
+      <c r="I144" s="15">
         <v>4.9863358168134653</v>
       </c>
     </row>
-    <row r="145" spans="2:9" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="32" t="s">
+    <row r="145" spans="2:14" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B145" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C145" s="18">
+      <c r="C145" s="16">
         <v>2010</v>
       </c>
-      <c r="D145" s="36">
+      <c r="D145" s="34">
         <v>675.27985999999999</v>
       </c>
-      <c r="E145" s="36">
+      <c r="E145" s="34">
         <v>659.54839000000004</v>
       </c>
-      <c r="F145" s="36">
+      <c r="F145" s="34">
         <v>1334.82825</v>
       </c>
-      <c r="G145" s="34">
+      <c r="G145" s="32">
         <v>17.354245878988959</v>
       </c>
-      <c r="H145" s="34">
+      <c r="H145" s="32">
         <v>16.359403957756633</v>
       </c>
-      <c r="I145" s="34">
+      <c r="I145" s="32">
         <v>16.848005964825198</v>
       </c>
     </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B146" s="41"/>
-    </row>
-    <row r="147" spans="2:9" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="C147" s="40"/>
-    </row>
-    <row r="148" spans="2:9" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B148" s="40" t="s">
+    <row r="146" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B146" s="39"/>
+    </row>
+    <row r="147" spans="2:14" s="42" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B147" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C147" s="55"/>
+      <c r="D147" s="55"/>
+      <c r="E147" s="55"/>
+      <c r="F147" s="55"/>
+      <c r="G147" s="55"/>
+      <c r="H147" s="55"/>
+      <c r="I147" s="55"/>
+      <c r="J147" s="55"/>
+      <c r="K147" s="55"/>
+      <c r="L147" s="55"/>
+      <c r="M147" s="56"/>
+      <c r="N147" s="56"/>
+    </row>
+    <row r="148" spans="2:14" s="42" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B148" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="C148" s="40"/>
-    </row>
-    <row r="149" spans="2:9" s="56" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="40" t="s">
+      <c r="C148" s="55"/>
+      <c r="D148" s="55"/>
+      <c r="E148" s="55"/>
+      <c r="F148" s="55"/>
+      <c r="G148" s="55"/>
+      <c r="H148" s="55"/>
+      <c r="I148" s="55"/>
+      <c r="J148" s="55"/>
+      <c r="K148" s="55"/>
+      <c r="L148" s="55"/>
+      <c r="M148" s="56"/>
+      <c r="N148" s="56"/>
+    </row>
+    <row r="149" spans="2:14" s="42" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B149" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C149" s="40"/>
-    </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B150" s="12" t="s">
+      <c r="C149" s="55"/>
+      <c r="D149" s="55"/>
+      <c r="E149" s="55"/>
+      <c r="F149" s="55"/>
+      <c r="G149" s="55"/>
+      <c r="H149" s="55"/>
+      <c r="I149" s="55"/>
+      <c r="J149" s="55"/>
+      <c r="K149" s="55"/>
+      <c r="L149" s="55"/>
+      <c r="M149" s="56"/>
+      <c r="N149" s="56"/>
+    </row>
+    <row r="150" spans="2:14" s="42" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B150" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C150" s="13"/>
-      <c r="D150" s="13"/>
-      <c r="E150" s="13"/>
-      <c r="F150" s="13"/>
-      <c r="G150" s="13"/>
-      <c r="H150" s="13"/>
-      <c r="I150" s="13"/>
-    </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B151" s="12"/>
-      <c r="C151" s="13"/>
-      <c r="D151" s="13"/>
-      <c r="E151" s="13"/>
-      <c r="F151" s="13"/>
-      <c r="G151" s="13"/>
-      <c r="H151" s="13"/>
-      <c r="I151" s="13"/>
-    </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B152" s="11" t="s">
+    </row>
+    <row r="151" spans="2:14" s="42" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B151" s="11"/>
+    </row>
+    <row r="152" spans="2:14" s="42" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B152" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C152" s="11"/>
-      <c r="D152" s="11"/>
-      <c r="E152" s="11"/>
-      <c r="F152" s="11"/>
-      <c r="G152" s="11"/>
-      <c r="H152" s="11"/>
-      <c r="I152" s="11"/>
-    </row>
-    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="2:14" s="42" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="2:14" s="42" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B154" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:14" s="42" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B155" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="156" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:14" s="42" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B156" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B157" s="14" t="s">
+    <row r="157" spans="2:14" s="42" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B157" s="12" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
+    <mergeCell ref="B147:L147"/>
+    <mergeCell ref="B148:L148"/>
+    <mergeCell ref="B149:L149"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="D6:I6"/>
@@ -4562,8 +4578,8 @@
     <mergeCell ref="G9:I9"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B157" r:id="rId1" xr:uid="{A0EBD9BD-CCB1-41CC-8657-AA4032C938C1}"/>
-    <hyperlink ref="B150" r:id="rId2" xr:uid="{211BF84A-1D3B-42B6-93E4-133DEF5CCC5B}"/>
+    <hyperlink ref="B150" r:id="rId1" xr:uid="{7818FA1F-D7B8-4125-898E-2432181C9E77}"/>
+    <hyperlink ref="B157" r:id="rId2" xr:uid="{6A28D4F4-0850-428A-99C7-BDC8F593FD40}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
